--- a/gia-cau-thu-bp.xlsx
+++ b/gia-cau-thu-bp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Tài liệu\FCOvv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F0C1BC-C075-4A37-BA5E-BCAC55CFA400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D707CAE-772D-4244-928A-0C298B953F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2268,7 +2268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>49</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>629693950895493</v>
       </c>
     </row>
-    <row r="4" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>31</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>718591920433680</v>
       </c>
     </row>
-    <row r="5" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>52</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>2024898195036490</v>
       </c>
     </row>
-    <row r="6" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>53</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>194390226723503</v>
       </c>
     </row>
-    <row r="7" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>51</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>476542504485538</v>
       </c>
     </row>
-    <row r="8" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>32</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>340775549896384</v>
       </c>
     </row>
-    <row r="9" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>236</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>793908255736867</v>
       </c>
     </row>
-    <row r="10" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>45895058406915</v>
       </c>
     </row>
-    <row r="11" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>50</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>802551113886413</v>
       </c>
     </row>
-    <row r="12" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>1</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>3160816694691100</v>
       </c>
     </row>
-    <row r="13" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>2679286026359250</v>
       </c>
     </row>
-    <row r="14" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>58</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>470418422139574</v>
       </c>
     </row>
-    <row r="15" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>34</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>231875537212105</v>
       </c>
     </row>
-    <row r="16" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>59</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>45436739986185</v>
       </c>
     </row>
-    <row r="17" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>54</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>963061336663695</v>
       </c>
     </row>
-    <row r="18" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>63</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>8909552058161</v>
       </c>
     </row>
-    <row r="19" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>57</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>47609801463785</v>
       </c>
     </row>
-    <row r="20" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>61</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>1196418506701440</v>
       </c>
     </row>
-    <row r="21" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>56</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>44547760290803</v>
       </c>
     </row>
-    <row r="22" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>6</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>848234792676870</v>
       </c>
     </row>
-    <row r="23" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>55</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>296326565127291</v>
       </c>
     </row>
-    <row r="24" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>33</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>2789173794260620</v>
       </c>
     </row>
-    <row r="25" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>4</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>238295946123196</v>
       </c>
     </row>
-    <row r="26" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>62</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>158040834734555</v>
       </c>
     </row>
-    <row r="27" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>60</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>884040919296418</v>
       </c>
     </row>
-    <row r="28" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>76</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>99763276926188</v>
       </c>
     </row>
-    <row r="29" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>9</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>107862869706334</v>
       </c>
     </row>
-    <row r="30" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>77</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>12712409643961</v>
       </c>
     </row>
-    <row r="31" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>66</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>1043316448052340</v>
       </c>
     </row>
-    <row r="32" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>78</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>39905310770475</v>
       </c>
     </row>
-    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>10</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>7008123265260</v>
       </c>
     </row>
-    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>8</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>617347010681856</v>
       </c>
     </row>
-    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>75</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>118530626050916</v>
       </c>
     </row>
-    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>1049489918159160</v>
       </c>
     </row>
-    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>64</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>471159238552392</v>
       </c>
     </row>
-    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>79</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>71315926673968</v>
       </c>
     </row>
-    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>69</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>729704166625954</v>
       </c>
     </row>
-    <row r="40" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>67</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>530918429186396</v>
       </c>
     </row>
-    <row r="41" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>68</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>548204145485488</v>
       </c>
     </row>
-    <row r="42" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>70</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>29632656512729</v>
       </c>
     </row>
-    <row r="43" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>38</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>449428623776391</v>
       </c>
     </row>
-    <row r="44" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>73</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>503755160716394</v>
       </c>
     </row>
-    <row r="45" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>80</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>15830752864317</v>
       </c>
     </row>
-    <row r="46" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>71</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>84551846582987</v>
       </c>
     </row>
-    <row r="47" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>74</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>57487353634694</v>
       </c>
     </row>
-    <row r="48" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>104998379576770</v>
       </c>
     </row>
-    <row r="49" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>72</v>
       </c>
@@ -8284,7 +8284,7 @@
         <v>401275556943206</v>
       </c>
     </row>
-    <row r="50" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>5</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>408683721071389</v>
       </c>
     </row>
-    <row r="51" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>35</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>617347010681856</v>
       </c>
     </row>
-    <row r="52" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>65</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>1000102157304610</v>
       </c>
     </row>
-    <row r="53" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>90</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>114579605182552</v>
       </c>
     </row>
-    <row r="54" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>83</v>
       </c>
@@ -8924,7 +8924,7 @@
         <v>229529618571514</v>
       </c>
     </row>
-    <row r="55" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>92</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>9126858205921</v>
       </c>
     </row>
-    <row r="56" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>98</v>
       </c>
@@ -9180,7 +9180,7 @@
         <v>38028575858002</v>
       </c>
     </row>
-    <row r="57" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>94</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>9778776649201</v>
       </c>
     </row>
-    <row r="58" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>82</v>
       </c>
@@ -9436,7 +9436,7 @@
         <v>71414702195677</v>
       </c>
     </row>
-    <row r="59" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>89</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>72896335021314</v>
       </c>
     </row>
-    <row r="60" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>91</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>64796742241168</v>
       </c>
     </row>
-    <row r="61" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>101</v>
       </c>
@@ -9820,7 +9820,7 @@
         <v>6682164043620</v>
       </c>
     </row>
-    <row r="62" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>81</v>
       </c>
@@ -9948,7 +9948,7 @@
         <v>56904578056611</v>
       </c>
     </row>
-    <row r="63" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>100</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>460540869968664</v>
       </c>
     </row>
-    <row r="64" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>40</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>1182836872466440</v>
       </c>
     </row>
-    <row r="65" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>86</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>11191266609641</v>
       </c>
     </row>
-    <row r="66" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>99</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>40201637335603</v>
       </c>
     </row>
-    <row r="67" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>85</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>118530626050916</v>
       </c>
     </row>
-    <row r="68" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>95</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>27064492948293</v>
       </c>
     </row>
-    <row r="69" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>88</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>320032690337474</v>
       </c>
     </row>
-    <row r="70" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>103</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>6736490580560</v>
       </c>
     </row>
-    <row r="71" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>102</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>36744494075784</v>
       </c>
     </row>
-    <row r="72" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>39</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>287683706977745</v>
       </c>
     </row>
-    <row r="73" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>43</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>93836745623642</v>
       </c>
     </row>
-    <row r="74" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>93</v>
       </c>
@@ -11484,7 +11484,7 @@
         <v>20644084037201</v>
       </c>
     </row>
-    <row r="75" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>87</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>83959193452732</v>
       </c>
     </row>
-    <row r="76" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>96</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>26471839818038</v>
       </c>
     </row>
-    <row r="77" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>41</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>92453888319715</v>
       </c>
     </row>
-    <row r="78" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>84</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>1140857275740070</v>
       </c>
     </row>
-    <row r="79" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>97</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>812428666057322</v>
       </c>
     </row>
-    <row r="80" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>119</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>52449802027531</v>
       </c>
     </row>
-    <row r="81" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>107</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>35559187815275</v>
       </c>
     </row>
-    <row r="82" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>120</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>31045146473169</v>
       </c>
     </row>
-    <row r="83" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>115</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>333490855170339</v>
       </c>
     </row>
-    <row r="84" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>113</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>508693936801849</v>
       </c>
     </row>
-    <row r="85" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>110</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>67266130283895</v>
       </c>
     </row>
-    <row r="86" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>118</v>
       </c>
@@ -13020,7 +13020,7 @@
         <v>28447350252220</v>
       </c>
     </row>
-    <row r="87" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>37</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>271632684700017</v>
       </c>
     </row>
-    <row r="88" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>108</v>
       </c>
@@ -13276,7 +13276,7 @@
         <v>276571460785471</v>
       </c>
     </row>
-    <row r="89" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>111</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>50494046697690</v>
       </c>
     </row>
-    <row r="90" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>109</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>56697149461022</v>
       </c>
     </row>
-    <row r="91" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>106</v>
       </c>
@@ -13660,7 +13660,7 @@
         <v>9941756260021</v>
       </c>
     </row>
-    <row r="92" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>112</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>62228578676731</v>
       </c>
     </row>
-    <row r="93" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>114</v>
       </c>
@@ -13916,7 +13916,7 @@
         <v>13798940382761</v>
       </c>
     </row>
-    <row r="94" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>117</v>
       </c>
@@ -14044,7 +14044,7 @@
         <v>18372247037892</v>
       </c>
     </row>
-    <row r="95" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>116</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>52252250984112</v>
       </c>
     </row>
-    <row r="96" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>105</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>26782982711422</v>
       </c>
     </row>
-    <row r="97" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>44</v>
       </c>
@@ -14428,7 +14428,7 @@
         <v>67167354762186</v>
       </c>
     </row>
-    <row r="98" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>48</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>7931674393240</v>
       </c>
     </row>
-    <row r="99" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>42</v>
       </c>
@@ -14684,7 +14684,7 @@
         <v>35756738858693</v>
       </c>
     </row>
-    <row r="100" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>121</v>
       </c>
@@ -14812,7 +14812,7 @@
         <v>41298045626573</v>
       </c>
     </row>
-    <row r="101" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>104</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>65562252534413</v>
       </c>
     </row>
-    <row r="102" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>237</v>
       </c>
@@ -15068,7 +15068,7 @@
         <v>11655511561673</v>
       </c>
     </row>
-    <row r="103" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>238</v>
       </c>
@@ -15196,7 +15196,7 @@
         <v>16110287590754</v>
       </c>
     </row>
-    <row r="104" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>47</v>
       </c>
@@ -15324,7 +15324,7 @@
         <v>15843593682139</v>
       </c>
     </row>
-    <row r="105" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>239</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>9344164353681</v>
       </c>
     </row>
-    <row r="106" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>240</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>23903676253602</v>
       </c>
     </row>
-    <row r="107" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>243</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>8257633614881</v>
       </c>
     </row>
-    <row r="108" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>244</v>
       </c>
@@ -15836,7 +15836,7 @@
         <v>27360819513420</v>
       </c>
     </row>
-    <row r="109" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>242</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>14223675126110</v>
       </c>
     </row>
-    <row r="110" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>245</v>
       </c>
@@ -16092,7 +16092,7 @@
         <v>14010813876827</v>
       </c>
     </row>
-    <row r="111" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>122</v>
       </c>
@@ -16220,7 +16220,7 @@
         <v>6410531358920</v>
       </c>
     </row>
-    <row r="112" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>246</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>14520001691237</v>
       </c>
     </row>
-    <row r="113" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>241</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>22530696501845</v>
       </c>
     </row>
-    <row r="114" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>258</v>
       </c>
@@ -16604,7 +16604,7 @@
         <v>12006164663741</v>
       </c>
     </row>
-    <row r="115" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>255</v>
       </c>
@@ -16732,7 +16732,7 @@
         <v>11788858515981</v>
       </c>
     </row>
-    <row r="116" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>257</v>
       </c>
@@ -16860,7 +16860,7 @@
         <v>8420613225701</v>
       </c>
     </row>
-    <row r="117" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>259</v>
       </c>
@@ -16988,7 +16988,7 @@
         <v>11951838126801</v>
       </c>
     </row>
-    <row r="118" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>256</v>
       </c>
@@ -17116,7 +17116,7 @@
         <v>9072531668981</v>
       </c>
     </row>
-    <row r="119" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>254</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>7225429413020</v>
       </c>
     </row>
-    <row r="120" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>260</v>
       </c>
@@ -17372,7 +17372,7 @@
         <v>11136940072701</v>
       </c>
     </row>
-    <row r="121" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>252</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>10267715481661</v>
       </c>
     </row>
-    <row r="122" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>253</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>9778776649201</v>
       </c>
     </row>
-    <row r="123" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>251</v>
       </c>
@@ -17756,7 +17756,7 @@
         <v>6519184432800</v>
       </c>
     </row>
-    <row r="124" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>261</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>4889388324600</v>
       </c>
     </row>
-    <row r="125" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>248</v>
       </c>
@@ -18012,7 +18012,7 @@
         <v>3802857585800</v>
       </c>
     </row>
-    <row r="126" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>249</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>6736490580560</v>
       </c>
     </row>
-    <row r="127" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>250</v>
       </c>
@@ -18268,7 +18268,7 @@
         <v>6627837506680</v>
       </c>
     </row>
-    <row r="128" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>247</v>
       </c>
@@ -41948,7 +41948,7 @@
         <v>37430983952</v>
       </c>
     </row>
-    <row r="313" spans="1:34" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:34" ht="22.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>324</v>
       </c>
@@ -41974,98 +41974,98 @@
         <v>30</v>
       </c>
       <c r="I313" s="3">
-        <f>$E313+0</f>
+        <f t="shared" ref="I313:I344" si="183">$E313+0</f>
         <v>124</v>
       </c>
       <c r="J313" s="14">
         <v>0</v>
       </c>
       <c r="K313" s="5">
-        <f>$E313+1</f>
+        <f t="shared" ref="K313:K344" si="184">$E313+1</f>
         <v>125</v>
       </c>
       <c r="L313" s="14">
         <v>0</v>
       </c>
       <c r="M313" s="3">
-        <f>$E313+2</f>
+        <f t="shared" ref="M313:M344" si="185">$E313+2</f>
         <v>126</v>
       </c>
       <c r="N313" s="14">
         <v>0</v>
       </c>
       <c r="O313" s="5">
-        <f>$E313+4</f>
+        <f t="shared" ref="O313:O344" si="186">$E313+4</f>
         <v>128</v>
       </c>
       <c r="P313" s="14">
         <v>0</v>
       </c>
       <c r="Q313" s="3">
-        <f>$E313+6</f>
+        <f t="shared" ref="Q313:Q344" si="187">$E313+6</f>
         <v>130</v>
       </c>
       <c r="R313" s="14">
         <v>0</v>
       </c>
       <c r="S313" s="5">
-        <f>$E313+8</f>
+        <f t="shared" ref="S313:S344" si="188">$E313+8</f>
         <v>132</v>
       </c>
       <c r="T313" s="14">
         <v>0</v>
       </c>
       <c r="U313" s="3">
-        <f>$E313+11</f>
+        <f t="shared" ref="U313:U344" si="189">$E313+11</f>
         <v>135</v>
       </c>
       <c r="V313" s="14">
         <v>0</v>
       </c>
       <c r="W313" s="5">
-        <f>$E313+15</f>
+        <f t="shared" ref="W313:W344" si="190">$E313+15</f>
         <v>139</v>
       </c>
       <c r="X313" s="14">
         <v>0</v>
       </c>
       <c r="Y313" s="3">
-        <f>$E313+17</f>
+        <f t="shared" ref="Y313:Y344" si="191">$E313+17</f>
         <v>141</v>
       </c>
       <c r="Z313" s="14">
         <v>0</v>
       </c>
       <c r="AA313" s="5">
-        <f>$E313+19</f>
+        <f t="shared" ref="AA313:AA344" si="192">$E313+19</f>
         <v>143</v>
       </c>
       <c r="AB313" s="14">
         <v>0</v>
       </c>
       <c r="AC313" s="3">
-        <f>$E313+21</f>
+        <f t="shared" ref="AC313:AC344" si="193">$E313+21</f>
         <v>145</v>
       </c>
       <c r="AD313" s="14">
         <v>0</v>
       </c>
       <c r="AE313" s="5">
-        <f>$E313+24</f>
+        <f t="shared" ref="AE313:AE344" si="194">$E313+24</f>
         <v>148</v>
       </c>
       <c r="AF313" s="14">
         <v>0</v>
       </c>
       <c r="AG313" s="3">
-        <f>$E313+27</f>
+        <f t="shared" ref="AG313:AG344" si="195">$E313+27</f>
         <v>151</v>
       </c>
       <c r="AH313" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>353</v>
       </c>
@@ -42091,74 +42091,74 @@
         <v>34</v>
       </c>
       <c r="I314" s="3">
-        <f>$E314+0</f>
+        <f t="shared" si="183"/>
         <v>131</v>
       </c>
       <c r="J314" s="14">
         <v>4800000000</v>
       </c>
       <c r="K314" s="5">
-        <f>$E314+1</f>
+        <f t="shared" si="184"/>
         <v>132</v>
       </c>
       <c r="L314" s="14"/>
       <c r="M314" s="3">
-        <f>$E314+2</f>
+        <f t="shared" si="185"/>
         <v>133</v>
       </c>
       <c r="N314" s="14"/>
       <c r="O314" s="5">
-        <f>$E314+4</f>
+        <f t="shared" si="186"/>
         <v>135</v>
       </c>
       <c r="P314" s="14"/>
       <c r="Q314" s="3">
-        <f>$E314+6</f>
+        <f t="shared" si="187"/>
         <v>137</v>
       </c>
       <c r="R314" s="14"/>
       <c r="S314" s="5">
-        <f>$E314+8</f>
+        <f t="shared" si="188"/>
         <v>139</v>
       </c>
       <c r="T314" s="14"/>
       <c r="U314" s="3">
-        <f>$E314+11</f>
+        <f t="shared" si="189"/>
         <v>142</v>
       </c>
       <c r="V314" s="14"/>
       <c r="W314" s="5">
-        <f>$E314+15</f>
+        <f t="shared" si="190"/>
         <v>146</v>
       </c>
       <c r="X314" s="14"/>
       <c r="Y314" s="3">
-        <f>$E314+17</f>
+        <f t="shared" si="191"/>
         <v>148</v>
       </c>
       <c r="Z314" s="14"/>
       <c r="AA314" s="5">
-        <f>$E314+19</f>
+        <f t="shared" si="192"/>
         <v>150</v>
       </c>
       <c r="AB314" s="14"/>
       <c r="AC314" s="3">
-        <f>$E314+21</f>
+        <f t="shared" si="193"/>
         <v>152</v>
       </c>
       <c r="AD314" s="14"/>
       <c r="AE314" s="5">
-        <f>$E314+24</f>
+        <f t="shared" si="194"/>
         <v>155</v>
       </c>
       <c r="AF314" s="14"/>
       <c r="AG314" s="3">
-        <f>$E314+27</f>
+        <f t="shared" si="195"/>
         <v>158</v>
       </c>
       <c r="AH314" s="14"/>
     </row>
-    <row r="315" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>354</v>
       </c>
@@ -42184,74 +42184,74 @@
         <v>33</v>
       </c>
       <c r="I315" s="3">
-        <f>$E315+0</f>
+        <f t="shared" si="183"/>
         <v>131</v>
       </c>
       <c r="J315" s="14">
         <v>3260000000</v>
       </c>
       <c r="K315" s="5">
-        <f>$E315+1</f>
+        <f t="shared" si="184"/>
         <v>132</v>
       </c>
       <c r="L315" s="14"/>
       <c r="M315" s="3">
-        <f>$E315+2</f>
+        <f t="shared" si="185"/>
         <v>133</v>
       </c>
       <c r="N315" s="14"/>
       <c r="O315" s="5">
-        <f>$E315+4</f>
+        <f t="shared" si="186"/>
         <v>135</v>
       </c>
       <c r="P315" s="14"/>
       <c r="Q315" s="3">
-        <f>$E315+6</f>
+        <f t="shared" si="187"/>
         <v>137</v>
       </c>
       <c r="R315" s="14"/>
       <c r="S315" s="5">
-        <f>$E315+8</f>
+        <f t="shared" si="188"/>
         <v>139</v>
       </c>
       <c r="T315" s="14"/>
       <c r="U315" s="3">
-        <f>$E315+11</f>
+        <f t="shared" si="189"/>
         <v>142</v>
       </c>
       <c r="V315" s="14"/>
       <c r="W315" s="5">
-        <f>$E315+15</f>
+        <f t="shared" si="190"/>
         <v>146</v>
       </c>
       <c r="X315" s="14"/>
       <c r="Y315" s="3">
-        <f>$E315+17</f>
+        <f t="shared" si="191"/>
         <v>148</v>
       </c>
       <c r="Z315" s="14"/>
       <c r="AA315" s="5">
-        <f>$E315+19</f>
+        <f t="shared" si="192"/>
         <v>150</v>
       </c>
       <c r="AB315" s="14"/>
       <c r="AC315" s="3">
-        <f>$E315+21</f>
+        <f t="shared" si="193"/>
         <v>152</v>
       </c>
       <c r="AD315" s="14"/>
       <c r="AE315" s="5">
-        <f>$E315+24</f>
+        <f t="shared" si="194"/>
         <v>155</v>
       </c>
       <c r="AF315" s="14"/>
       <c r="AG315" s="3">
-        <f>$E315+27</f>
+        <f t="shared" si="195"/>
         <v>158</v>
       </c>
       <c r="AH315" s="14"/>
     </row>
-    <row r="316" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>355</v>
       </c>
@@ -42277,74 +42277,74 @@
         <v>35</v>
       </c>
       <c r="I316" s="3">
-        <f>$E316+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J316" s="14">
         <v>11600000000</v>
       </c>
       <c r="K316" s="5">
-        <f>$E316+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L316" s="14"/>
       <c r="M316" s="3">
-        <f>$E316+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N316" s="14"/>
       <c r="O316" s="5">
-        <f>$E316+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P316" s="14"/>
       <c r="Q316" s="3">
-        <f>$E316+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R316" s="14"/>
       <c r="S316" s="5">
-        <f>$E316+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T316" s="14"/>
       <c r="U316" s="3">
-        <f>$E316+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V316" s="14"/>
       <c r="W316" s="5">
-        <f>$E316+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X316" s="14"/>
       <c r="Y316" s="3">
-        <f>$E316+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z316" s="14"/>
       <c r="AA316" s="5">
-        <f>$E316+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB316" s="14"/>
       <c r="AC316" s="3">
-        <f>$E316+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD316" s="14"/>
       <c r="AE316" s="5">
-        <f>$E316+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF316" s="14"/>
       <c r="AG316" s="3">
-        <f>$E316+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH316" s="14"/>
     </row>
-    <row r="317" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>356</v>
       </c>
@@ -42370,74 +42370,74 @@
         <v>35</v>
       </c>
       <c r="I317" s="3">
-        <f>$E317+0</f>
+        <f t="shared" si="183"/>
         <v>134</v>
       </c>
       <c r="J317" s="14">
         <v>7440000000</v>
       </c>
       <c r="K317" s="5">
-        <f>$E317+1</f>
+        <f t="shared" si="184"/>
         <v>135</v>
       </c>
       <c r="L317" s="14"/>
       <c r="M317" s="3">
-        <f>$E317+2</f>
+        <f t="shared" si="185"/>
         <v>136</v>
       </c>
       <c r="N317" s="14"/>
       <c r="O317" s="5">
-        <f>$E317+4</f>
+        <f t="shared" si="186"/>
         <v>138</v>
       </c>
       <c r="P317" s="14"/>
       <c r="Q317" s="3">
-        <f>$E317+6</f>
+        <f t="shared" si="187"/>
         <v>140</v>
       </c>
       <c r="R317" s="14"/>
       <c r="S317" s="5">
-        <f>$E317+8</f>
+        <f t="shared" si="188"/>
         <v>142</v>
       </c>
       <c r="T317" s="14"/>
       <c r="U317" s="3">
-        <f>$E317+11</f>
+        <f t="shared" si="189"/>
         <v>145</v>
       </c>
       <c r="V317" s="14"/>
       <c r="W317" s="5">
-        <f>$E317+15</f>
+        <f t="shared" si="190"/>
         <v>149</v>
       </c>
       <c r="X317" s="14"/>
       <c r="Y317" s="3">
-        <f>$E317+17</f>
+        <f t="shared" si="191"/>
         <v>151</v>
       </c>
       <c r="Z317" s="14"/>
       <c r="AA317" s="5">
-        <f>$E317+19</f>
+        <f t="shared" si="192"/>
         <v>153</v>
       </c>
       <c r="AB317" s="14"/>
       <c r="AC317" s="3">
-        <f>$E317+21</f>
+        <f t="shared" si="193"/>
         <v>155</v>
       </c>
       <c r="AD317" s="14"/>
       <c r="AE317" s="5">
-        <f>$E317+24</f>
+        <f t="shared" si="194"/>
         <v>158</v>
       </c>
       <c r="AF317" s="14"/>
       <c r="AG317" s="3">
-        <f>$E317+27</f>
+        <f t="shared" si="195"/>
         <v>161</v>
       </c>
       <c r="AH317" s="14"/>
     </row>
-    <row r="318" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>357</v>
       </c>
@@ -42463,74 +42463,74 @@
         <v>36</v>
       </c>
       <c r="I318" s="3">
-        <f>$E318+0</f>
+        <f t="shared" si="183"/>
         <v>136</v>
       </c>
       <c r="J318" s="14">
         <v>22800000000</v>
       </c>
       <c r="K318" s="5">
-        <f>$E318+1</f>
+        <f t="shared" si="184"/>
         <v>137</v>
       </c>
       <c r="L318" s="14"/>
       <c r="M318" s="3">
-        <f>$E318+2</f>
+        <f t="shared" si="185"/>
         <v>138</v>
       </c>
       <c r="N318" s="14"/>
       <c r="O318" s="5">
-        <f>$E318+4</f>
+        <f t="shared" si="186"/>
         <v>140</v>
       </c>
       <c r="P318" s="14"/>
       <c r="Q318" s="3">
-        <f>$E318+6</f>
+        <f t="shared" si="187"/>
         <v>142</v>
       </c>
       <c r="R318" s="14"/>
       <c r="S318" s="5">
-        <f>$E318+8</f>
+        <f t="shared" si="188"/>
         <v>144</v>
       </c>
       <c r="T318" s="14"/>
       <c r="U318" s="3">
-        <f>$E318+11</f>
+        <f t="shared" si="189"/>
         <v>147</v>
       </c>
       <c r="V318" s="14"/>
       <c r="W318" s="5">
-        <f>$E318+15</f>
+        <f t="shared" si="190"/>
         <v>151</v>
       </c>
       <c r="X318" s="14"/>
       <c r="Y318" s="3">
-        <f>$E318+17</f>
+        <f t="shared" si="191"/>
         <v>153</v>
       </c>
       <c r="Z318" s="14"/>
       <c r="AA318" s="5">
-        <f>$E318+19</f>
+        <f t="shared" si="192"/>
         <v>155</v>
       </c>
       <c r="AB318" s="14"/>
       <c r="AC318" s="3">
-        <f>$E318+21</f>
+        <f t="shared" si="193"/>
         <v>157</v>
       </c>
       <c r="AD318" s="14"/>
       <c r="AE318" s="5">
-        <f>$E318+24</f>
+        <f t="shared" si="194"/>
         <v>160</v>
       </c>
       <c r="AF318" s="14"/>
       <c r="AG318" s="3">
-        <f>$E318+27</f>
+        <f t="shared" si="195"/>
         <v>163</v>
       </c>
       <c r="AH318" s="14"/>
     </row>
-    <row r="319" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>329</v>
       </c>
@@ -42556,74 +42556,74 @@
         <v>32</v>
       </c>
       <c r="I319" s="3">
-        <f>$E319+0</f>
+        <f t="shared" si="183"/>
         <v>129</v>
       </c>
       <c r="J319" s="14">
         <v>7440000000</v>
       </c>
       <c r="K319" s="5">
-        <f>$E319+1</f>
+        <f t="shared" si="184"/>
         <v>130</v>
       </c>
       <c r="L319" s="14"/>
       <c r="M319" s="3">
-        <f>$E319+2</f>
+        <f t="shared" si="185"/>
         <v>131</v>
       </c>
       <c r="N319" s="14"/>
       <c r="O319" s="5">
-        <f>$E319+4</f>
+        <f t="shared" si="186"/>
         <v>133</v>
       </c>
       <c r="P319" s="14"/>
       <c r="Q319" s="3">
-        <f>$E319+6</f>
+        <f t="shared" si="187"/>
         <v>135</v>
       </c>
       <c r="R319" s="14"/>
       <c r="S319" s="5">
-        <f>$E319+8</f>
+        <f t="shared" si="188"/>
         <v>137</v>
       </c>
       <c r="T319" s="14"/>
       <c r="U319" s="3">
-        <f>$E319+11</f>
+        <f t="shared" si="189"/>
         <v>140</v>
       </c>
       <c r="V319" s="14"/>
       <c r="W319" s="5">
-        <f>$E319+15</f>
+        <f t="shared" si="190"/>
         <v>144</v>
       </c>
       <c r="X319" s="14"/>
       <c r="Y319" s="3">
-        <f>$E319+17</f>
+        <f t="shared" si="191"/>
         <v>146</v>
       </c>
       <c r="Z319" s="14"/>
       <c r="AA319" s="5">
-        <f>$E319+19</f>
+        <f t="shared" si="192"/>
         <v>148</v>
       </c>
       <c r="AB319" s="14"/>
       <c r="AC319" s="3">
-        <f>$E319+21</f>
+        <f t="shared" si="193"/>
         <v>150</v>
       </c>
       <c r="AD319" s="14"/>
       <c r="AE319" s="5">
-        <f>$E319+24</f>
+        <f t="shared" si="194"/>
         <v>153</v>
       </c>
       <c r="AF319" s="14"/>
       <c r="AG319" s="3">
-        <f>$E319+27</f>
+        <f t="shared" si="195"/>
         <v>156</v>
       </c>
       <c r="AH319" s="14"/>
     </row>
-    <row r="320" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>330</v>
       </c>
@@ -42649,74 +42649,74 @@
         <v>34</v>
       </c>
       <c r="I320" s="3">
-        <f>$E320+0</f>
+        <f t="shared" si="183"/>
         <v>132</v>
       </c>
       <c r="J320" s="14">
         <v>7840000000</v>
       </c>
       <c r="K320" s="5">
-        <f>$E320+1</f>
+        <f t="shared" si="184"/>
         <v>133</v>
       </c>
       <c r="L320" s="14"/>
       <c r="M320" s="3">
-        <f>$E320+2</f>
+        <f t="shared" si="185"/>
         <v>134</v>
       </c>
       <c r="N320" s="14"/>
       <c r="O320" s="5">
-        <f>$E320+4</f>
+        <f t="shared" si="186"/>
         <v>136</v>
       </c>
       <c r="P320" s="14"/>
       <c r="Q320" s="3">
-        <f>$E320+6</f>
+        <f t="shared" si="187"/>
         <v>138</v>
       </c>
       <c r="R320" s="14"/>
       <c r="S320" s="5">
-        <f>$E320+8</f>
+        <f t="shared" si="188"/>
         <v>140</v>
       </c>
       <c r="T320" s="14"/>
       <c r="U320" s="3">
-        <f>$E320+11</f>
+        <f t="shared" si="189"/>
         <v>143</v>
       </c>
       <c r="V320" s="14"/>
       <c r="W320" s="5">
-        <f>$E320+15</f>
+        <f t="shared" si="190"/>
         <v>147</v>
       </c>
       <c r="X320" s="14"/>
       <c r="Y320" s="3">
-        <f>$E320+17</f>
+        <f t="shared" si="191"/>
         <v>149</v>
       </c>
       <c r="Z320" s="14"/>
       <c r="AA320" s="5">
-        <f>$E320+19</f>
+        <f t="shared" si="192"/>
         <v>151</v>
       </c>
       <c r="AB320" s="14"/>
       <c r="AC320" s="3">
-        <f>$E320+21</f>
+        <f t="shared" si="193"/>
         <v>153</v>
       </c>
       <c r="AD320" s="14"/>
       <c r="AE320" s="5">
-        <f>$E320+24</f>
+        <f t="shared" si="194"/>
         <v>156</v>
       </c>
       <c r="AF320" s="14"/>
       <c r="AG320" s="3">
-        <f>$E320+27</f>
+        <f t="shared" si="195"/>
         <v>159</v>
       </c>
       <c r="AH320" s="14"/>
     </row>
-    <row r="321" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>331</v>
       </c>
@@ -42742,74 +42742,74 @@
         <v>35</v>
       </c>
       <c r="I321" s="3">
-        <f>$E321+0</f>
+        <f t="shared" si="183"/>
         <v>132</v>
       </c>
       <c r="J321" s="14">
         <v>5180000000</v>
       </c>
       <c r="K321" s="5">
-        <f>$E321+1</f>
+        <f t="shared" si="184"/>
         <v>133</v>
       </c>
       <c r="L321" s="14"/>
       <c r="M321" s="3">
-        <f>$E321+2</f>
+        <f t="shared" si="185"/>
         <v>134</v>
       </c>
       <c r="N321" s="14"/>
       <c r="O321" s="5">
-        <f>$E321+4</f>
+        <f t="shared" si="186"/>
         <v>136</v>
       </c>
       <c r="P321" s="14"/>
       <c r="Q321" s="3">
-        <f>$E321+6</f>
+        <f t="shared" si="187"/>
         <v>138</v>
       </c>
       <c r="R321" s="14"/>
       <c r="S321" s="5">
-        <f>$E321+8</f>
+        <f t="shared" si="188"/>
         <v>140</v>
       </c>
       <c r="T321" s="14"/>
       <c r="U321" s="3">
-        <f>$E321+11</f>
+        <f t="shared" si="189"/>
         <v>143</v>
       </c>
       <c r="V321" s="14"/>
       <c r="W321" s="5">
-        <f>$E321+15</f>
+        <f t="shared" si="190"/>
         <v>147</v>
       </c>
       <c r="X321" s="14"/>
       <c r="Y321" s="3">
-        <f>$E321+17</f>
+        <f t="shared" si="191"/>
         <v>149</v>
       </c>
       <c r="Z321" s="14"/>
       <c r="AA321" s="5">
-        <f>$E321+19</f>
+        <f t="shared" si="192"/>
         <v>151</v>
       </c>
       <c r="AB321" s="14"/>
       <c r="AC321" s="3">
-        <f>$E321+21</f>
+        <f t="shared" si="193"/>
         <v>153</v>
       </c>
       <c r="AD321" s="14"/>
       <c r="AE321" s="5">
-        <f>$E321+24</f>
+        <f t="shared" si="194"/>
         <v>156</v>
       </c>
       <c r="AF321" s="14"/>
       <c r="AG321" s="3">
-        <f>$E321+27</f>
+        <f t="shared" si="195"/>
         <v>159</v>
       </c>
       <c r="AH321" s="14"/>
     </row>
-    <row r="322" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>332</v>
       </c>
@@ -42835,74 +42835,74 @@
         <v>35</v>
       </c>
       <c r="I322" s="3">
-        <f>$E322+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J322" s="14">
         <v>5600000000</v>
       </c>
       <c r="K322" s="5">
-        <f>$E322+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L322" s="14"/>
       <c r="M322" s="3">
-        <f>$E322+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N322" s="14"/>
       <c r="O322" s="5">
-        <f>$E322+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P322" s="14"/>
       <c r="Q322" s="3">
-        <f>$E322+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R322" s="14"/>
       <c r="S322" s="5">
-        <f>$E322+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T322" s="14"/>
       <c r="U322" s="3">
-        <f>$E322+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V322" s="14"/>
       <c r="W322" s="5">
-        <f>$E322+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X322" s="14"/>
       <c r="Y322" s="3">
-        <f>$E322+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z322" s="14"/>
       <c r="AA322" s="5">
-        <f>$E322+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB322" s="14"/>
       <c r="AC322" s="3">
-        <f>$E322+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD322" s="14"/>
       <c r="AE322" s="5">
-        <f>$E322+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF322" s="14"/>
       <c r="AG322" s="3">
-        <f>$E322+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH322" s="14"/>
     </row>
-    <row r="323" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>333</v>
       </c>
@@ -42928,74 +42928,74 @@
         <v>34</v>
       </c>
       <c r="I323" s="3">
-        <f>$E323+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J323" s="14">
         <v>7840000000</v>
       </c>
       <c r="K323" s="5">
-        <f>$E323+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L323" s="14"/>
       <c r="M323" s="3">
-        <f>$E323+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N323" s="14"/>
       <c r="O323" s="5">
-        <f>$E323+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P323" s="14"/>
       <c r="Q323" s="3">
-        <f>$E323+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R323" s="14"/>
       <c r="S323" s="5">
-        <f>$E323+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T323" s="14"/>
       <c r="U323" s="3">
-        <f>$E323+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V323" s="14"/>
       <c r="W323" s="5">
-        <f>$E323+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X323" s="14"/>
       <c r="Y323" s="3">
-        <f>$E323+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z323" s="14"/>
       <c r="AA323" s="5">
-        <f>$E323+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB323" s="14"/>
       <c r="AC323" s="3">
-        <f>$E323+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD323" s="14"/>
       <c r="AE323" s="5">
-        <f>$E323+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF323" s="14"/>
       <c r="AG323" s="3">
-        <f>$E323+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH323" s="14"/>
     </row>
-    <row r="324" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>334</v>
       </c>
@@ -43021,74 +43021,74 @@
         <v>34</v>
       </c>
       <c r="I324" s="3">
-        <f>$E324+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J324" s="14">
         <v>5980000000</v>
       </c>
       <c r="K324" s="5">
-        <f>$E324+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L324" s="14"/>
       <c r="M324" s="3">
-        <f>$E324+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N324" s="14"/>
       <c r="O324" s="5">
-        <f>$E324+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P324" s="14"/>
       <c r="Q324" s="3">
-        <f>$E324+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R324" s="14"/>
       <c r="S324" s="5">
-        <f>$E324+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T324" s="14"/>
       <c r="U324" s="3">
-        <f>$E324+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V324" s="14"/>
       <c r="W324" s="5">
-        <f>$E324+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X324" s="14"/>
       <c r="Y324" s="3">
-        <f>$E324+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z324" s="14"/>
       <c r="AA324" s="5">
-        <f>$E324+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB324" s="14"/>
       <c r="AC324" s="3">
-        <f>$E324+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD324" s="14"/>
       <c r="AE324" s="5">
-        <f>$E324+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF324" s="14"/>
       <c r="AG324" s="3">
-        <f>$E324+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH324" s="14"/>
     </row>
-    <row r="325" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>335</v>
       </c>
@@ -43114,74 +43114,74 @@
         <v>37</v>
       </c>
       <c r="I325" s="3">
-        <f>$E325+0</f>
+        <f t="shared" si="183"/>
         <v>135</v>
       </c>
       <c r="J325" s="14">
         <v>5000000000</v>
       </c>
       <c r="K325" s="5">
-        <f>$E325+1</f>
+        <f t="shared" si="184"/>
         <v>136</v>
       </c>
       <c r="L325" s="14"/>
       <c r="M325" s="3">
-        <f>$E325+2</f>
+        <f t="shared" si="185"/>
         <v>137</v>
       </c>
       <c r="N325" s="14"/>
       <c r="O325" s="5">
-        <f>$E325+4</f>
+        <f t="shared" si="186"/>
         <v>139</v>
       </c>
       <c r="P325" s="14"/>
       <c r="Q325" s="3">
-        <f>$E325+6</f>
+        <f t="shared" si="187"/>
         <v>141</v>
       </c>
       <c r="R325" s="14"/>
       <c r="S325" s="5">
-        <f>$E325+8</f>
+        <f t="shared" si="188"/>
         <v>143</v>
       </c>
       <c r="T325" s="14"/>
       <c r="U325" s="3">
-        <f>$E325+11</f>
+        <f t="shared" si="189"/>
         <v>146</v>
       </c>
       <c r="V325" s="14"/>
       <c r="W325" s="5">
-        <f>$E325+15</f>
+        <f t="shared" si="190"/>
         <v>150</v>
       </c>
       <c r="X325" s="14"/>
       <c r="Y325" s="3">
-        <f>$E325+17</f>
+        <f t="shared" si="191"/>
         <v>152</v>
       </c>
       <c r="Z325" s="14"/>
       <c r="AA325" s="5">
-        <f>$E325+19</f>
+        <f t="shared" si="192"/>
         <v>154</v>
       </c>
       <c r="AB325" s="14"/>
       <c r="AC325" s="3">
-        <f>$E325+21</f>
+        <f t="shared" si="193"/>
         <v>156</v>
       </c>
       <c r="AD325" s="14"/>
       <c r="AE325" s="5">
-        <f>$E325+24</f>
+        <f t="shared" si="194"/>
         <v>159</v>
       </c>
       <c r="AF325" s="14"/>
       <c r="AG325" s="3">
-        <f>$E325+27</f>
+        <f t="shared" si="195"/>
         <v>162</v>
       </c>
       <c r="AH325" s="14"/>
     </row>
-    <row r="326" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>336</v>
       </c>
@@ -43207,74 +43207,74 @@
         <v>36</v>
       </c>
       <c r="I326" s="3">
-        <f>$E326+0</f>
+        <f t="shared" si="183"/>
         <v>135</v>
       </c>
       <c r="J326" s="14">
         <v>11600000000</v>
       </c>
       <c r="K326" s="5">
-        <f>$E326+1</f>
+        <f t="shared" si="184"/>
         <v>136</v>
       </c>
       <c r="L326" s="14"/>
       <c r="M326" s="3">
-        <f>$E326+2</f>
+        <f t="shared" si="185"/>
         <v>137</v>
       </c>
       <c r="N326" s="14"/>
       <c r="O326" s="5">
-        <f>$E326+4</f>
+        <f t="shared" si="186"/>
         <v>139</v>
       </c>
       <c r="P326" s="14"/>
       <c r="Q326" s="3">
-        <f>$E326+6</f>
+        <f t="shared" si="187"/>
         <v>141</v>
       </c>
       <c r="R326" s="14"/>
       <c r="S326" s="5">
-        <f>$E326+8</f>
+        <f t="shared" si="188"/>
         <v>143</v>
       </c>
       <c r="T326" s="14"/>
       <c r="U326" s="3">
-        <f>$E326+11</f>
+        <f t="shared" si="189"/>
         <v>146</v>
       </c>
       <c r="V326" s="14"/>
       <c r="W326" s="5">
-        <f>$E326+15</f>
+        <f t="shared" si="190"/>
         <v>150</v>
       </c>
       <c r="X326" s="14"/>
       <c r="Y326" s="3">
-        <f>$E326+17</f>
+        <f t="shared" si="191"/>
         <v>152</v>
       </c>
       <c r="Z326" s="14"/>
       <c r="AA326" s="5">
-        <f>$E326+19</f>
+        <f t="shared" si="192"/>
         <v>154</v>
       </c>
       <c r="AB326" s="14"/>
       <c r="AC326" s="3">
-        <f>$E326+21</f>
+        <f t="shared" si="193"/>
         <v>156</v>
       </c>
       <c r="AD326" s="14"/>
       <c r="AE326" s="5">
-        <f>$E326+24</f>
+        <f t="shared" si="194"/>
         <v>159</v>
       </c>
       <c r="AF326" s="14"/>
       <c r="AG326" s="3">
-        <f>$E326+27</f>
+        <f t="shared" si="195"/>
         <v>162</v>
       </c>
       <c r="AH326" s="14"/>
     </row>
-    <row r="327" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>337</v>
       </c>
@@ -43300,74 +43300,74 @@
         <v>37</v>
       </c>
       <c r="I327" s="3">
-        <f>$E327+0</f>
+        <f t="shared" si="183"/>
         <v>136</v>
       </c>
       <c r="J327" s="14">
         <v>32800000000</v>
       </c>
       <c r="K327" s="5">
-        <f>$E327+1</f>
+        <f t="shared" si="184"/>
         <v>137</v>
       </c>
       <c r="L327" s="14"/>
       <c r="M327" s="3">
-        <f>$E327+2</f>
+        <f t="shared" si="185"/>
         <v>138</v>
       </c>
       <c r="N327" s="14"/>
       <c r="O327" s="5">
-        <f>$E327+4</f>
+        <f t="shared" si="186"/>
         <v>140</v>
       </c>
       <c r="P327" s="14"/>
       <c r="Q327" s="3">
-        <f>$E327+6</f>
+        <f t="shared" si="187"/>
         <v>142</v>
       </c>
       <c r="R327" s="14"/>
       <c r="S327" s="5">
-        <f>$E327+8</f>
+        <f t="shared" si="188"/>
         <v>144</v>
       </c>
       <c r="T327" s="14"/>
       <c r="U327" s="3">
-        <f>$E327+11</f>
+        <f t="shared" si="189"/>
         <v>147</v>
       </c>
       <c r="V327" s="14"/>
       <c r="W327" s="5">
-        <f>$E327+15</f>
+        <f t="shared" si="190"/>
         <v>151</v>
       </c>
       <c r="X327" s="14"/>
       <c r="Y327" s="3">
-        <f>$E327+17</f>
+        <f t="shared" si="191"/>
         <v>153</v>
       </c>
       <c r="Z327" s="14"/>
       <c r="AA327" s="5">
-        <f>$E327+19</f>
+        <f t="shared" si="192"/>
         <v>155</v>
       </c>
       <c r="AB327" s="14"/>
       <c r="AC327" s="3">
-        <f>$E327+21</f>
+        <f t="shared" si="193"/>
         <v>157</v>
       </c>
       <c r="AD327" s="14"/>
       <c r="AE327" s="5">
-        <f>$E327+24</f>
+        <f t="shared" si="194"/>
         <v>160</v>
       </c>
       <c r="AF327" s="14"/>
       <c r="AG327" s="3">
-        <f>$E327+27</f>
+        <f t="shared" si="195"/>
         <v>163</v>
       </c>
       <c r="AH327" s="14"/>
     </row>
-    <row r="328" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>340</v>
       </c>
@@ -43393,74 +43393,74 @@
         <v>34</v>
       </c>
       <c r="I328" s="3">
-        <f>$E328+0</f>
+        <f t="shared" si="183"/>
         <v>131</v>
       </c>
       <c r="J328" s="14">
         <v>16900000000</v>
       </c>
       <c r="K328" s="5">
-        <f>$E328+1</f>
+        <f t="shared" si="184"/>
         <v>132</v>
       </c>
       <c r="L328" s="14"/>
       <c r="M328" s="3">
-        <f>$E328+2</f>
+        <f t="shared" si="185"/>
         <v>133</v>
       </c>
       <c r="N328" s="14"/>
       <c r="O328" s="5">
-        <f>$E328+4</f>
+        <f t="shared" si="186"/>
         <v>135</v>
       </c>
       <c r="P328" s="14"/>
       <c r="Q328" s="3">
-        <f>$E328+6</f>
+        <f t="shared" si="187"/>
         <v>137</v>
       </c>
       <c r="R328" s="14"/>
       <c r="S328" s="5">
-        <f>$E328+8</f>
+        <f t="shared" si="188"/>
         <v>139</v>
       </c>
       <c r="T328" s="14"/>
       <c r="U328" s="3">
-        <f>$E328+11</f>
+        <f t="shared" si="189"/>
         <v>142</v>
       </c>
       <c r="V328" s="14"/>
       <c r="W328" s="5">
-        <f>$E328+15</f>
+        <f t="shared" si="190"/>
         <v>146</v>
       </c>
       <c r="X328" s="14"/>
       <c r="Y328" s="3">
-        <f>$E328+17</f>
+        <f t="shared" si="191"/>
         <v>148</v>
       </c>
       <c r="Z328" s="14"/>
       <c r="AA328" s="5">
-        <f>$E328+19</f>
+        <f t="shared" si="192"/>
         <v>150</v>
       </c>
       <c r="AB328" s="14"/>
       <c r="AC328" s="3">
-        <f>$E328+21</f>
+        <f t="shared" si="193"/>
         <v>152</v>
       </c>
       <c r="AD328" s="14"/>
       <c r="AE328" s="5">
-        <f>$E328+24</f>
+        <f t="shared" si="194"/>
         <v>155</v>
       </c>
       <c r="AF328" s="14"/>
       <c r="AG328" s="3">
-        <f>$E328+27</f>
+        <f t="shared" si="195"/>
         <v>158</v>
       </c>
       <c r="AH328" s="14"/>
     </row>
-    <row r="329" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>341</v>
       </c>
@@ -43486,74 +43486,74 @@
         <v>34</v>
       </c>
       <c r="I329" s="3">
-        <f>$E329+0</f>
+        <f t="shared" si="183"/>
         <v>132</v>
       </c>
       <c r="J329" s="14">
         <v>8840000000</v>
       </c>
       <c r="K329" s="5">
-        <f>$E329+1</f>
+        <f t="shared" si="184"/>
         <v>133</v>
       </c>
       <c r="L329" s="14"/>
       <c r="M329" s="3">
-        <f>$E329+2</f>
+        <f t="shared" si="185"/>
         <v>134</v>
       </c>
       <c r="N329" s="14"/>
       <c r="O329" s="5">
-        <f>$E329+4</f>
+        <f t="shared" si="186"/>
         <v>136</v>
       </c>
       <c r="P329" s="14"/>
       <c r="Q329" s="3">
-        <f>$E329+6</f>
+        <f t="shared" si="187"/>
         <v>138</v>
       </c>
       <c r="R329" s="14"/>
       <c r="S329" s="5">
-        <f>$E329+8</f>
+        <f t="shared" si="188"/>
         <v>140</v>
       </c>
       <c r="T329" s="14"/>
       <c r="U329" s="3">
-        <f>$E329+11</f>
+        <f t="shared" si="189"/>
         <v>143</v>
       </c>
       <c r="V329" s="14"/>
       <c r="W329" s="5">
-        <f>$E329+15</f>
+        <f t="shared" si="190"/>
         <v>147</v>
       </c>
       <c r="X329" s="14"/>
       <c r="Y329" s="3">
-        <f>$E329+17</f>
+        <f t="shared" si="191"/>
         <v>149</v>
       </c>
       <c r="Z329" s="14"/>
       <c r="AA329" s="5">
-        <f>$E329+19</f>
+        <f t="shared" si="192"/>
         <v>151</v>
       </c>
       <c r="AB329" s="14"/>
       <c r="AC329" s="3">
-        <f>$E329+21</f>
+        <f t="shared" si="193"/>
         <v>153</v>
       </c>
       <c r="AD329" s="14"/>
       <c r="AE329" s="5">
-        <f>$E329+24</f>
+        <f t="shared" si="194"/>
         <v>156</v>
       </c>
       <c r="AF329" s="14"/>
       <c r="AG329" s="3">
-        <f>$E329+27</f>
+        <f t="shared" si="195"/>
         <v>159</v>
       </c>
       <c r="AH329" s="14"/>
     </row>
-    <row r="330" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>342</v>
       </c>
@@ -43579,74 +43579,74 @@
         <v>35</v>
       </c>
       <c r="I330" s="3">
-        <f>$E330+0</f>
+        <f t="shared" si="183"/>
         <v>134</v>
       </c>
       <c r="J330" s="14">
         <v>21500000000</v>
       </c>
       <c r="K330" s="5">
-        <f>$E330+1</f>
+        <f t="shared" si="184"/>
         <v>135</v>
       </c>
       <c r="L330" s="14"/>
       <c r="M330" s="3">
-        <f>$E330+2</f>
+        <f t="shared" si="185"/>
         <v>136</v>
       </c>
       <c r="N330" s="14"/>
       <c r="O330" s="5">
-        <f>$E330+4</f>
+        <f t="shared" si="186"/>
         <v>138</v>
       </c>
       <c r="P330" s="14"/>
       <c r="Q330" s="3">
-        <f>$E330+6</f>
+        <f t="shared" si="187"/>
         <v>140</v>
       </c>
       <c r="R330" s="14"/>
       <c r="S330" s="5">
-        <f>$E330+8</f>
+        <f t="shared" si="188"/>
         <v>142</v>
       </c>
       <c r="T330" s="14"/>
       <c r="U330" s="3">
-        <f>$E330+11</f>
+        <f t="shared" si="189"/>
         <v>145</v>
       </c>
       <c r="V330" s="14"/>
       <c r="W330" s="5">
-        <f>$E330+15</f>
+        <f t="shared" si="190"/>
         <v>149</v>
       </c>
       <c r="X330" s="14"/>
       <c r="Y330" s="3">
-        <f>$E330+17</f>
+        <f t="shared" si="191"/>
         <v>151</v>
       </c>
       <c r="Z330" s="14"/>
       <c r="AA330" s="5">
-        <f>$E330+19</f>
+        <f t="shared" si="192"/>
         <v>153</v>
       </c>
       <c r="AB330" s="14"/>
       <c r="AC330" s="3">
-        <f>$E330+21</f>
+        <f t="shared" si="193"/>
         <v>155</v>
       </c>
       <c r="AD330" s="14"/>
       <c r="AE330" s="5">
-        <f>$E330+24</f>
+        <f t="shared" si="194"/>
         <v>158</v>
       </c>
       <c r="AF330" s="14"/>
       <c r="AG330" s="3">
-        <f>$E330+27</f>
+        <f t="shared" si="195"/>
         <v>161</v>
       </c>
       <c r="AH330" s="14"/>
     </row>
-    <row r="331" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>343</v>
       </c>
@@ -43672,74 +43672,74 @@
         <v>36</v>
       </c>
       <c r="I331" s="3">
-        <f>$E331+0</f>
+        <f t="shared" si="183"/>
         <v>135</v>
       </c>
       <c r="J331" s="14">
         <v>18600000000</v>
       </c>
       <c r="K331" s="5">
-        <f>$E331+1</f>
+        <f t="shared" si="184"/>
         <v>136</v>
       </c>
       <c r="L331" s="14"/>
       <c r="M331" s="3">
-        <f>$E331+2</f>
+        <f t="shared" si="185"/>
         <v>137</v>
       </c>
       <c r="N331" s="14"/>
       <c r="O331" s="5">
-        <f>$E331+4</f>
+        <f t="shared" si="186"/>
         <v>139</v>
       </c>
       <c r="P331" s="14"/>
       <c r="Q331" s="3">
-        <f>$E331+6</f>
+        <f t="shared" si="187"/>
         <v>141</v>
       </c>
       <c r="R331" s="14"/>
       <c r="S331" s="5">
-        <f>$E331+8</f>
+        <f t="shared" si="188"/>
         <v>143</v>
       </c>
       <c r="T331" s="14"/>
       <c r="U331" s="3">
-        <f>$E331+11</f>
+        <f t="shared" si="189"/>
         <v>146</v>
       </c>
       <c r="V331" s="14"/>
       <c r="W331" s="5">
-        <f>$E331+15</f>
+        <f t="shared" si="190"/>
         <v>150</v>
       </c>
       <c r="X331" s="14"/>
       <c r="Y331" s="3">
-        <f>$E331+17</f>
+        <f t="shared" si="191"/>
         <v>152</v>
       </c>
       <c r="Z331" s="14"/>
       <c r="AA331" s="5">
-        <f>$E331+19</f>
+        <f t="shared" si="192"/>
         <v>154</v>
       </c>
       <c r="AB331" s="14"/>
       <c r="AC331" s="3">
-        <f>$E331+21</f>
+        <f t="shared" si="193"/>
         <v>156</v>
       </c>
       <c r="AD331" s="14"/>
       <c r="AE331" s="5">
-        <f>$E331+24</f>
+        <f t="shared" si="194"/>
         <v>159</v>
       </c>
       <c r="AF331" s="14"/>
       <c r="AG331" s="3">
-        <f>$E331+27</f>
+        <f t="shared" si="195"/>
         <v>162</v>
       </c>
       <c r="AH331" s="14"/>
     </row>
-    <row r="332" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>358</v>
       </c>
@@ -43765,74 +43765,74 @@
         <v>35</v>
       </c>
       <c r="I332" s="3">
-        <f>$E332+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J332" s="14">
         <v>9600000000</v>
       </c>
       <c r="K332" s="5">
-        <f>$E332+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L332" s="14"/>
       <c r="M332" s="3">
-        <f>$E332+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N332" s="14"/>
       <c r="O332" s="5">
-        <f>$E332+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P332" s="14"/>
       <c r="Q332" s="3">
-        <f>$E332+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R332" s="14"/>
       <c r="S332" s="5">
-        <f>$E332+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T332" s="14"/>
       <c r="U332" s="3">
-        <f>$E332+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V332" s="14"/>
       <c r="W332" s="5">
-        <f>$E332+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X332" s="14"/>
       <c r="Y332" s="3">
-        <f>$E332+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z332" s="14"/>
       <c r="AA332" s="5">
-        <f>$E332+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB332" s="14"/>
       <c r="AC332" s="3">
-        <f>$E332+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD332" s="14"/>
       <c r="AE332" s="5">
-        <f>$E332+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF332" s="14"/>
       <c r="AG332" s="3">
-        <f>$E332+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH332" s="14"/>
     </row>
-    <row r="333" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>359</v>
       </c>
@@ -43858,74 +43858,74 @@
         <v>38</v>
       </c>
       <c r="I333" s="3">
-        <f>$E333+0</f>
+        <f t="shared" si="183"/>
         <v>136</v>
       </c>
       <c r="J333" s="14">
         <v>14700000000</v>
       </c>
       <c r="K333" s="5">
-        <f>$E333+1</f>
+        <f t="shared" si="184"/>
         <v>137</v>
       </c>
       <c r="L333" s="14"/>
       <c r="M333" s="3">
-        <f>$E333+2</f>
+        <f t="shared" si="185"/>
         <v>138</v>
       </c>
       <c r="N333" s="14"/>
       <c r="O333" s="5">
-        <f>$E333+4</f>
+        <f t="shared" si="186"/>
         <v>140</v>
       </c>
       <c r="P333" s="14"/>
       <c r="Q333" s="3">
-        <f>$E333+6</f>
+        <f t="shared" si="187"/>
         <v>142</v>
       </c>
       <c r="R333" s="14"/>
       <c r="S333" s="5">
-        <f>$E333+8</f>
+        <f t="shared" si="188"/>
         <v>144</v>
       </c>
       <c r="T333" s="14"/>
       <c r="U333" s="3">
-        <f>$E333+11</f>
+        <f t="shared" si="189"/>
         <v>147</v>
       </c>
       <c r="V333" s="14"/>
       <c r="W333" s="5">
-        <f>$E333+15</f>
+        <f t="shared" si="190"/>
         <v>151</v>
       </c>
       <c r="X333" s="14"/>
       <c r="Y333" s="3">
-        <f>$E333+17</f>
+        <f t="shared" si="191"/>
         <v>153</v>
       </c>
       <c r="Z333" s="14"/>
       <c r="AA333" s="5">
-        <f>$E333+19</f>
+        <f t="shared" si="192"/>
         <v>155</v>
       </c>
       <c r="AB333" s="14"/>
       <c r="AC333" s="3">
-        <f>$E333+21</f>
+        <f t="shared" si="193"/>
         <v>157</v>
       </c>
       <c r="AD333" s="14"/>
       <c r="AE333" s="5">
-        <f>$E333+24</f>
+        <f t="shared" si="194"/>
         <v>160</v>
       </c>
       <c r="AF333" s="14"/>
       <c r="AG333" s="3">
-        <f>$E333+27</f>
+        <f t="shared" si="195"/>
         <v>163</v>
       </c>
       <c r="AH333" s="14"/>
     </row>
-    <row r="334" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>323</v>
       </c>
@@ -43951,98 +43951,98 @@
         <v>29</v>
       </c>
       <c r="I334" s="3">
-        <f>$E334+0</f>
+        <f t="shared" si="183"/>
         <v>124</v>
       </c>
       <c r="J334" s="14">
         <v>0</v>
       </c>
       <c r="K334" s="5">
-        <f>$E334+1</f>
+        <f t="shared" si="184"/>
         <v>125</v>
       </c>
       <c r="L334" s="14">
         <v>0</v>
       </c>
       <c r="M334" s="3">
-        <f>$E334+2</f>
+        <f t="shared" si="185"/>
         <v>126</v>
       </c>
       <c r="N334" s="14">
         <v>0</v>
       </c>
       <c r="O334" s="5">
-        <f>$E334+4</f>
+        <f t="shared" si="186"/>
         <v>128</v>
       </c>
       <c r="P334" s="14">
         <v>0</v>
       </c>
       <c r="Q334" s="3">
-        <f>$E334+6</f>
+        <f t="shared" si="187"/>
         <v>130</v>
       </c>
       <c r="R334" s="14">
         <v>0</v>
       </c>
       <c r="S334" s="5">
-        <f>$E334+8</f>
+        <f t="shared" si="188"/>
         <v>132</v>
       </c>
       <c r="T334" s="14">
         <v>0</v>
       </c>
       <c r="U334" s="3">
-        <f>$E334+11</f>
+        <f t="shared" si="189"/>
         <v>135</v>
       </c>
       <c r="V334" s="14">
         <v>0</v>
       </c>
       <c r="W334" s="5">
-        <f>$E334+15</f>
+        <f t="shared" si="190"/>
         <v>139</v>
       </c>
       <c r="X334" s="14">
         <v>0</v>
       </c>
       <c r="Y334" s="3">
-        <f>$E334+17</f>
+        <f t="shared" si="191"/>
         <v>141</v>
       </c>
       <c r="Z334" s="14">
         <v>0</v>
       </c>
       <c r="AA334" s="5">
-        <f>$E334+19</f>
+        <f t="shared" si="192"/>
         <v>143</v>
       </c>
       <c r="AB334" s="14">
         <v>0</v>
       </c>
       <c r="AC334" s="3">
-        <f>$E334+21</f>
+        <f t="shared" si="193"/>
         <v>145</v>
       </c>
       <c r="AD334" s="14">
         <v>0</v>
       </c>
       <c r="AE334" s="5">
-        <f>$E334+24</f>
+        <f t="shared" si="194"/>
         <v>148</v>
       </c>
       <c r="AF334" s="14">
         <v>0</v>
       </c>
       <c r="AG334" s="3">
-        <f>$E334+27</f>
+        <f t="shared" si="195"/>
         <v>151</v>
       </c>
       <c r="AH334" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>345</v>
       </c>
@@ -44068,74 +44068,74 @@
         <v>31</v>
       </c>
       <c r="I335" s="3">
-        <f>$E335+0</f>
+        <f t="shared" si="183"/>
         <v>128</v>
       </c>
       <c r="J335" s="14">
         <v>21500000000</v>
       </c>
       <c r="K335" s="5">
-        <f>$E335+1</f>
+        <f t="shared" si="184"/>
         <v>129</v>
       </c>
       <c r="L335" s="14"/>
       <c r="M335" s="3">
-        <f>$E335+2</f>
+        <f t="shared" si="185"/>
         <v>130</v>
       </c>
       <c r="N335" s="14"/>
       <c r="O335" s="5">
-        <f>$E335+4</f>
+        <f t="shared" si="186"/>
         <v>132</v>
       </c>
       <c r="P335" s="14"/>
       <c r="Q335" s="3">
-        <f>$E335+6</f>
+        <f t="shared" si="187"/>
         <v>134</v>
       </c>
       <c r="R335" s="14"/>
       <c r="S335" s="5">
-        <f>$E335+8</f>
+        <f t="shared" si="188"/>
         <v>136</v>
       </c>
       <c r="T335" s="14"/>
       <c r="U335" s="3">
-        <f>$E335+11</f>
+        <f t="shared" si="189"/>
         <v>139</v>
       </c>
       <c r="V335" s="14"/>
       <c r="W335" s="5">
-        <f>$E335+15</f>
+        <f t="shared" si="190"/>
         <v>143</v>
       </c>
       <c r="X335" s="14"/>
       <c r="Y335" s="3">
-        <f>$E335+17</f>
+        <f t="shared" si="191"/>
         <v>145</v>
       </c>
       <c r="Z335" s="14"/>
       <c r="AA335" s="5">
-        <f>$E335+19</f>
+        <f t="shared" si="192"/>
         <v>147</v>
       </c>
       <c r="AB335" s="14"/>
       <c r="AC335" s="3">
-        <f>$E335+21</f>
+        <f t="shared" si="193"/>
         <v>149</v>
       </c>
       <c r="AD335" s="14"/>
       <c r="AE335" s="5">
-        <f>$E335+24</f>
+        <f t="shared" si="194"/>
         <v>152</v>
       </c>
       <c r="AF335" s="14"/>
       <c r="AG335" s="3">
-        <f>$E335+27</f>
+        <f t="shared" si="195"/>
         <v>155</v>
       </c>
       <c r="AH335" s="14"/>
     </row>
-    <row r="336" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>346</v>
       </c>
@@ -44161,74 +44161,74 @@
         <v>36</v>
       </c>
       <c r="I336" s="3">
-        <f>$E336+0</f>
+        <f t="shared" si="183"/>
         <v>134</v>
       </c>
       <c r="J336" s="14">
         <v>11700000000</v>
       </c>
       <c r="K336" s="5">
-        <f>$E336+1</f>
+        <f t="shared" si="184"/>
         <v>135</v>
       </c>
       <c r="L336" s="14"/>
       <c r="M336" s="3">
-        <f>$E336+2</f>
+        <f t="shared" si="185"/>
         <v>136</v>
       </c>
       <c r="N336" s="14"/>
       <c r="O336" s="5">
-        <f>$E336+4</f>
+        <f t="shared" si="186"/>
         <v>138</v>
       </c>
       <c r="P336" s="14"/>
       <c r="Q336" s="3">
-        <f>$E336+6</f>
+        <f t="shared" si="187"/>
         <v>140</v>
       </c>
       <c r="R336" s="14"/>
       <c r="S336" s="5">
-        <f>$E336+8</f>
+        <f t="shared" si="188"/>
         <v>142</v>
       </c>
       <c r="T336" s="14"/>
       <c r="U336" s="3">
-        <f>$E336+11</f>
+        <f t="shared" si="189"/>
         <v>145</v>
       </c>
       <c r="V336" s="14"/>
       <c r="W336" s="5">
-        <f>$E336+15</f>
+        <f t="shared" si="190"/>
         <v>149</v>
       </c>
       <c r="X336" s="14"/>
       <c r="Y336" s="3">
-        <f>$E336+17</f>
+        <f t="shared" si="191"/>
         <v>151</v>
       </c>
       <c r="Z336" s="14"/>
       <c r="AA336" s="5">
-        <f>$E336+19</f>
+        <f t="shared" si="192"/>
         <v>153</v>
       </c>
       <c r="AB336" s="14"/>
       <c r="AC336" s="3">
-        <f>$E336+21</f>
+        <f t="shared" si="193"/>
         <v>155</v>
       </c>
       <c r="AD336" s="14"/>
       <c r="AE336" s="5">
-        <f>$E336+24</f>
+        <f t="shared" si="194"/>
         <v>158</v>
       </c>
       <c r="AF336" s="14"/>
       <c r="AG336" s="3">
-        <f>$E336+27</f>
+        <f t="shared" si="195"/>
         <v>161</v>
       </c>
       <c r="AH336" s="14"/>
     </row>
-    <row r="337" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>347</v>
       </c>
@@ -44254,74 +44254,74 @@
         <v>36</v>
       </c>
       <c r="I337" s="3">
-        <f>$E337+0</f>
+        <f t="shared" si="183"/>
         <v>134</v>
       </c>
       <c r="J337" s="14">
         <v>15000000000</v>
       </c>
       <c r="K337" s="5">
-        <f>$E337+1</f>
+        <f t="shared" si="184"/>
         <v>135</v>
       </c>
       <c r="L337" s="14"/>
       <c r="M337" s="3">
-        <f>$E337+2</f>
+        <f t="shared" si="185"/>
         <v>136</v>
       </c>
       <c r="N337" s="14"/>
       <c r="O337" s="5">
-        <f>$E337+4</f>
+        <f t="shared" si="186"/>
         <v>138</v>
       </c>
       <c r="P337" s="14"/>
       <c r="Q337" s="3">
-        <f>$E337+6</f>
+        <f t="shared" si="187"/>
         <v>140</v>
       </c>
       <c r="R337" s="14"/>
       <c r="S337" s="5">
-        <f>$E337+8</f>
+        <f t="shared" si="188"/>
         <v>142</v>
       </c>
       <c r="T337" s="14"/>
       <c r="U337" s="3">
-        <f>$E337+11</f>
+        <f t="shared" si="189"/>
         <v>145</v>
       </c>
       <c r="V337" s="14"/>
       <c r="W337" s="5">
-        <f>$E337+15</f>
+        <f t="shared" si="190"/>
         <v>149</v>
       </c>
       <c r="X337" s="14"/>
       <c r="Y337" s="3">
-        <f>$E337+17</f>
+        <f t="shared" si="191"/>
         <v>151</v>
       </c>
       <c r="Z337" s="14"/>
       <c r="AA337" s="5">
-        <f>$E337+19</f>
+        <f t="shared" si="192"/>
         <v>153</v>
       </c>
       <c r="AB337" s="14"/>
       <c r="AC337" s="3">
-        <f>$E337+21</f>
+        <f t="shared" si="193"/>
         <v>155</v>
       </c>
       <c r="AD337" s="14"/>
       <c r="AE337" s="5">
-        <f>$E337+24</f>
+        <f t="shared" si="194"/>
         <v>158</v>
       </c>
       <c r="AF337" s="14"/>
       <c r="AG337" s="3">
-        <f>$E337+27</f>
+        <f t="shared" si="195"/>
         <v>161</v>
       </c>
       <c r="AH337" s="14"/>
     </row>
-    <row r="338" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>348</v>
       </c>
@@ -44347,74 +44347,74 @@
         <v>36</v>
       </c>
       <c r="I338" s="3">
-        <f>$E338+0</f>
+        <f t="shared" si="183"/>
         <v>134</v>
       </c>
       <c r="J338" s="14">
         <v>21400000000</v>
       </c>
       <c r="K338" s="5">
-        <f>$E338+1</f>
+        <f t="shared" si="184"/>
         <v>135</v>
       </c>
       <c r="L338" s="14"/>
       <c r="M338" s="3">
-        <f>$E338+2</f>
+        <f t="shared" si="185"/>
         <v>136</v>
       </c>
       <c r="N338" s="14"/>
       <c r="O338" s="5">
-        <f>$E338+4</f>
+        <f t="shared" si="186"/>
         <v>138</v>
       </c>
       <c r="P338" s="14"/>
       <c r="Q338" s="3">
-        <f>$E338+6</f>
+        <f t="shared" si="187"/>
         <v>140</v>
       </c>
       <c r="R338" s="14"/>
       <c r="S338" s="5">
-        <f>$E338+8</f>
+        <f t="shared" si="188"/>
         <v>142</v>
       </c>
       <c r="T338" s="14"/>
       <c r="U338" s="3">
-        <f>$E338+11</f>
+        <f t="shared" si="189"/>
         <v>145</v>
       </c>
       <c r="V338" s="14"/>
       <c r="W338" s="5">
-        <f>$E338+15</f>
+        <f t="shared" si="190"/>
         <v>149</v>
       </c>
       <c r="X338" s="14"/>
       <c r="Y338" s="3">
-        <f>$E338+17</f>
+        <f t="shared" si="191"/>
         <v>151</v>
       </c>
       <c r="Z338" s="14"/>
       <c r="AA338" s="5">
-        <f>$E338+19</f>
+        <f t="shared" si="192"/>
         <v>153</v>
       </c>
       <c r="AB338" s="14"/>
       <c r="AC338" s="3">
-        <f>$E338+21</f>
+        <f t="shared" si="193"/>
         <v>155</v>
       </c>
       <c r="AD338" s="14"/>
       <c r="AE338" s="5">
-        <f>$E338+24</f>
+        <f t="shared" si="194"/>
         <v>158</v>
       </c>
       <c r="AF338" s="14"/>
       <c r="AG338" s="3">
-        <f>$E338+27</f>
+        <f t="shared" si="195"/>
         <v>161</v>
       </c>
       <c r="AH338" s="14"/>
     </row>
-    <row r="339" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="2">
         <v>349</v>
       </c>
@@ -44440,74 +44440,74 @@
         <v>35</v>
       </c>
       <c r="I339" s="3">
-        <f>$E339+0</f>
+        <f t="shared" si="183"/>
         <v>135</v>
       </c>
       <c r="J339" s="14">
         <v>14800000000</v>
       </c>
       <c r="K339" s="5">
-        <f>$E339+1</f>
+        <f t="shared" si="184"/>
         <v>136</v>
       </c>
       <c r="L339" s="14"/>
       <c r="M339" s="3">
-        <f>$E339+2</f>
+        <f t="shared" si="185"/>
         <v>137</v>
       </c>
       <c r="N339" s="14"/>
       <c r="O339" s="5">
-        <f>$E339+4</f>
+        <f t="shared" si="186"/>
         <v>139</v>
       </c>
       <c r="P339" s="14"/>
       <c r="Q339" s="3">
-        <f>$E339+6</f>
+        <f t="shared" si="187"/>
         <v>141</v>
       </c>
       <c r="R339" s="14"/>
       <c r="S339" s="5">
-        <f>$E339+8</f>
+        <f t="shared" si="188"/>
         <v>143</v>
       </c>
       <c r="T339" s="14"/>
       <c r="U339" s="3">
-        <f>$E339+11</f>
+        <f t="shared" si="189"/>
         <v>146</v>
       </c>
       <c r="V339" s="14"/>
       <c r="W339" s="5">
-        <f>$E339+15</f>
+        <f t="shared" si="190"/>
         <v>150</v>
       </c>
       <c r="X339" s="14"/>
       <c r="Y339" s="3">
-        <f>$E339+17</f>
+        <f t="shared" si="191"/>
         <v>152</v>
       </c>
       <c r="Z339" s="14"/>
       <c r="AA339" s="5">
-        <f>$E339+19</f>
+        <f t="shared" si="192"/>
         <v>154</v>
       </c>
       <c r="AB339" s="14"/>
       <c r="AC339" s="3">
-        <f>$E339+21</f>
+        <f t="shared" si="193"/>
         <v>156</v>
       </c>
       <c r="AD339" s="14"/>
       <c r="AE339" s="5">
-        <f>$E339+24</f>
+        <f t="shared" si="194"/>
         <v>159</v>
       </c>
       <c r="AF339" s="14"/>
       <c r="AG339" s="3">
-        <f>$E339+27</f>
+        <f t="shared" si="195"/>
         <v>162</v>
       </c>
       <c r="AH339" s="14"/>
     </row>
-    <row r="340" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="2">
         <v>325</v>
       </c>
@@ -44533,74 +44533,74 @@
         <v>30</v>
       </c>
       <c r="I340" s="3">
-        <f>$E340+0</f>
+        <f t="shared" si="183"/>
         <v>130</v>
       </c>
       <c r="J340" s="14">
         <v>2800000000</v>
       </c>
       <c r="K340" s="5">
-        <f>$E340+1</f>
+        <f t="shared" si="184"/>
         <v>131</v>
       </c>
       <c r="L340" s="14"/>
       <c r="M340" s="3">
-        <f>$E340+2</f>
+        <f t="shared" si="185"/>
         <v>132</v>
       </c>
       <c r="N340" s="14"/>
       <c r="O340" s="5">
-        <f>$E340+4</f>
+        <f t="shared" si="186"/>
         <v>134</v>
       </c>
       <c r="P340" s="14"/>
       <c r="Q340" s="3">
-        <f>$E340+6</f>
+        <f t="shared" si="187"/>
         <v>136</v>
       </c>
       <c r="R340" s="14"/>
       <c r="S340" s="5">
-        <f>$E340+8</f>
+        <f t="shared" si="188"/>
         <v>138</v>
       </c>
       <c r="T340" s="14"/>
       <c r="U340" s="3">
-        <f>$E340+11</f>
+        <f t="shared" si="189"/>
         <v>141</v>
       </c>
       <c r="V340" s="14"/>
       <c r="W340" s="5">
-        <f>$E340+15</f>
+        <f t="shared" si="190"/>
         <v>145</v>
       </c>
       <c r="X340" s="14"/>
       <c r="Y340" s="3">
-        <f>$E340+17</f>
+        <f t="shared" si="191"/>
         <v>147</v>
       </c>
       <c r="Z340" s="14"/>
       <c r="AA340" s="5">
-        <f>$E340+19</f>
+        <f t="shared" si="192"/>
         <v>149</v>
       </c>
       <c r="AB340" s="14"/>
       <c r="AC340" s="3">
-        <f>$E340+21</f>
+        <f t="shared" si="193"/>
         <v>151</v>
       </c>
       <c r="AD340" s="14"/>
       <c r="AE340" s="5">
-        <f>$E340+24</f>
+        <f t="shared" si="194"/>
         <v>154</v>
       </c>
       <c r="AF340" s="14"/>
       <c r="AG340" s="3">
-        <f>$E340+27</f>
+        <f t="shared" si="195"/>
         <v>157</v>
       </c>
       <c r="AH340" s="14"/>
     </row>
-    <row r="341" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="2">
         <v>326</v>
       </c>
@@ -44626,74 +44626,74 @@
         <v>32</v>
       </c>
       <c r="I341" s="3">
-        <f>$E341+0</f>
+        <f t="shared" si="183"/>
         <v>133</v>
       </c>
       <c r="J341" s="14">
         <v>8840000000</v>
       </c>
       <c r="K341" s="5">
-        <f>$E341+1</f>
+        <f t="shared" si="184"/>
         <v>134</v>
       </c>
       <c r="L341" s="14"/>
       <c r="M341" s="3">
-        <f>$E341+2</f>
+        <f t="shared" si="185"/>
         <v>135</v>
       </c>
       <c r="N341" s="14"/>
       <c r="O341" s="5">
-        <f>$E341+4</f>
+        <f t="shared" si="186"/>
         <v>137</v>
       </c>
       <c r="P341" s="14"/>
       <c r="Q341" s="3">
-        <f>$E341+6</f>
+        <f t="shared" si="187"/>
         <v>139</v>
       </c>
       <c r="R341" s="14"/>
       <c r="S341" s="5">
-        <f>$E341+8</f>
+        <f t="shared" si="188"/>
         <v>141</v>
       </c>
       <c r="T341" s="14"/>
       <c r="U341" s="3">
-        <f>$E341+11</f>
+        <f t="shared" si="189"/>
         <v>144</v>
       </c>
       <c r="V341" s="14"/>
       <c r="W341" s="5">
-        <f>$E341+15</f>
+        <f t="shared" si="190"/>
         <v>148</v>
       </c>
       <c r="X341" s="14"/>
       <c r="Y341" s="3">
-        <f>$E341+17</f>
+        <f t="shared" si="191"/>
         <v>150</v>
       </c>
       <c r="Z341" s="14"/>
       <c r="AA341" s="5">
-        <f>$E341+19</f>
+        <f t="shared" si="192"/>
         <v>152</v>
       </c>
       <c r="AB341" s="14"/>
       <c r="AC341" s="3">
-        <f>$E341+21</f>
+        <f t="shared" si="193"/>
         <v>154</v>
       </c>
       <c r="AD341" s="14"/>
       <c r="AE341" s="5">
-        <f>$E341+24</f>
+        <f t="shared" si="194"/>
         <v>157</v>
       </c>
       <c r="AF341" s="14"/>
       <c r="AG341" s="3">
-        <f>$E341+27</f>
+        <f t="shared" si="195"/>
         <v>160</v>
       </c>
       <c r="AH341" s="14"/>
     </row>
-    <row r="342" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="2">
         <v>327</v>
       </c>
@@ -44719,74 +44719,74 @@
         <v>33</v>
       </c>
       <c r="I342" s="3">
-        <f>$E342+0</f>
+        <f t="shared" si="183"/>
         <v>136</v>
       </c>
       <c r="J342" s="14">
         <v>12800000000</v>
       </c>
       <c r="K342" s="5">
-        <f>$E342+1</f>
+        <f t="shared" si="184"/>
         <v>137</v>
       </c>
       <c r="L342" s="14"/>
       <c r="M342" s="3">
-        <f>$E342+2</f>
+        <f t="shared" si="185"/>
         <v>138</v>
       </c>
       <c r="N342" s="14"/>
       <c r="O342" s="5">
-        <f>$E342+4</f>
+        <f t="shared" si="186"/>
         <v>140</v>
       </c>
       <c r="P342" s="14"/>
       <c r="Q342" s="3">
-        <f>$E342+6</f>
+        <f t="shared" si="187"/>
         <v>142</v>
       </c>
       <c r="R342" s="14"/>
       <c r="S342" s="5">
-        <f>$E342+8</f>
+        <f t="shared" si="188"/>
         <v>144</v>
       </c>
       <c r="T342" s="14"/>
       <c r="U342" s="3">
-        <f>$E342+11</f>
+        <f t="shared" si="189"/>
         <v>147</v>
       </c>
       <c r="V342" s="14"/>
       <c r="W342" s="5">
-        <f>$E342+15</f>
+        <f t="shared" si="190"/>
         <v>151</v>
       </c>
       <c r="X342" s="14"/>
       <c r="Y342" s="3">
-        <f>$E342+17</f>
+        <f t="shared" si="191"/>
         <v>153</v>
       </c>
       <c r="Z342" s="14"/>
       <c r="AA342" s="5">
-        <f>$E342+19</f>
+        <f t="shared" si="192"/>
         <v>155</v>
       </c>
       <c r="AB342" s="14"/>
       <c r="AC342" s="3">
-        <f>$E342+21</f>
+        <f t="shared" si="193"/>
         <v>157</v>
       </c>
       <c r="AD342" s="14"/>
       <c r="AE342" s="5">
-        <f>$E342+24</f>
+        <f t="shared" si="194"/>
         <v>160</v>
       </c>
       <c r="AF342" s="14"/>
       <c r="AG342" s="3">
-        <f>$E342+27</f>
+        <f t="shared" si="195"/>
         <v>163</v>
       </c>
       <c r="AH342" s="14"/>
     </row>
-    <row r="343" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2">
         <v>338</v>
       </c>
@@ -44812,74 +44812,74 @@
         <v>36</v>
       </c>
       <c r="I343" s="3">
-        <f>$E343+0</f>
+        <f t="shared" si="183"/>
         <v>135</v>
       </c>
       <c r="J343" s="14">
         <v>9600000000</v>
       </c>
       <c r="K343" s="5">
-        <f>$E343+1</f>
+        <f t="shared" si="184"/>
         <v>136</v>
       </c>
       <c r="L343" s="14"/>
       <c r="M343" s="3">
-        <f>$E343+2</f>
+        <f t="shared" si="185"/>
         <v>137</v>
       </c>
       <c r="N343" s="14"/>
       <c r="O343" s="5">
-        <f>$E343+4</f>
+        <f t="shared" si="186"/>
         <v>139</v>
       </c>
       <c r="P343" s="14"/>
       <c r="Q343" s="3">
-        <f>$E343+6</f>
+        <f t="shared" si="187"/>
         <v>141</v>
       </c>
       <c r="R343" s="14"/>
       <c r="S343" s="5">
-        <f>$E343+8</f>
+        <f t="shared" si="188"/>
         <v>143</v>
       </c>
       <c r="T343" s="14"/>
       <c r="U343" s="3">
-        <f>$E343+11</f>
+        <f t="shared" si="189"/>
         <v>146</v>
       </c>
       <c r="V343" s="14"/>
       <c r="W343" s="5">
-        <f>$E343+15</f>
+        <f t="shared" si="190"/>
         <v>150</v>
       </c>
       <c r="X343" s="14"/>
       <c r="Y343" s="3">
-        <f>$E343+17</f>
+        <f t="shared" si="191"/>
         <v>152</v>
       </c>
       <c r="Z343" s="14"/>
       <c r="AA343" s="5">
-        <f>$E343+19</f>
+        <f t="shared" si="192"/>
         <v>154</v>
       </c>
       <c r="AB343" s="14"/>
       <c r="AC343" s="3">
-        <f>$E343+21</f>
+        <f t="shared" si="193"/>
         <v>156</v>
       </c>
       <c r="AD343" s="14"/>
       <c r="AE343" s="5">
-        <f>$E343+24</f>
+        <f t="shared" si="194"/>
         <v>159</v>
       </c>
       <c r="AF343" s="14"/>
       <c r="AG343" s="3">
-        <f>$E343+27</f>
+        <f t="shared" si="195"/>
         <v>162</v>
       </c>
       <c r="AH343" s="14"/>
     </row>
-    <row r="344" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="2">
         <v>339</v>
       </c>
@@ -44905,74 +44905,74 @@
         <v>37</v>
       </c>
       <c r="I344" s="3">
-        <f>$E344+0</f>
+        <f t="shared" si="183"/>
         <v>136</v>
       </c>
       <c r="J344" s="14">
         <v>15600000000</v>
       </c>
       <c r="K344" s="5">
-        <f>$E344+1</f>
+        <f t="shared" si="184"/>
         <v>137</v>
       </c>
       <c r="L344" s="14"/>
       <c r="M344" s="3">
-        <f>$E344+2</f>
+        <f t="shared" si="185"/>
         <v>138</v>
       </c>
       <c r="N344" s="14"/>
       <c r="O344" s="5">
-        <f>$E344+4</f>
+        <f t="shared" si="186"/>
         <v>140</v>
       </c>
       <c r="P344" s="14"/>
       <c r="Q344" s="3">
-        <f>$E344+6</f>
+        <f t="shared" si="187"/>
         <v>142</v>
       </c>
       <c r="R344" s="14"/>
       <c r="S344" s="5">
-        <f>$E344+8</f>
+        <f t="shared" si="188"/>
         <v>144</v>
       </c>
       <c r="T344" s="14"/>
       <c r="U344" s="3">
-        <f>$E344+11</f>
+        <f t="shared" si="189"/>
         <v>147</v>
       </c>
       <c r="V344" s="14"/>
       <c r="W344" s="5">
-        <f>$E344+15</f>
+        <f t="shared" si="190"/>
         <v>151</v>
       </c>
       <c r="X344" s="14"/>
       <c r="Y344" s="3">
-        <f>$E344+17</f>
+        <f t="shared" si="191"/>
         <v>153</v>
       </c>
       <c r="Z344" s="14"/>
       <c r="AA344" s="5">
-        <f>$E344+19</f>
+        <f t="shared" si="192"/>
         <v>155</v>
       </c>
       <c r="AB344" s="14"/>
       <c r="AC344" s="3">
-        <f>$E344+21</f>
+        <f t="shared" si="193"/>
         <v>157</v>
       </c>
       <c r="AD344" s="14"/>
       <c r="AE344" s="5">
-        <f>$E344+24</f>
+        <f t="shared" si="194"/>
         <v>160</v>
       </c>
       <c r="AF344" s="14"/>
       <c r="AG344" s="3">
-        <f>$E344+27</f>
+        <f t="shared" si="195"/>
         <v>163</v>
       </c>
       <c r="AH344" s="14"/>
     </row>
-    <row r="345" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>350</v>
       </c>
@@ -44998,74 +44998,74 @@
         <v>32</v>
       </c>
       <c r="I345" s="3">
-        <f>$E345+0</f>
+        <f t="shared" ref="I345:I372" si="196">$E345+0</f>
         <v>129</v>
       </c>
       <c r="J345" s="14">
         <v>3650000000</v>
       </c>
       <c r="K345" s="5">
-        <f>$E345+1</f>
+        <f t="shared" ref="K345:K372" si="197">$E345+1</f>
         <v>130</v>
       </c>
       <c r="L345" s="14"/>
       <c r="M345" s="3">
-        <f>$E345+2</f>
+        <f t="shared" ref="M345:M372" si="198">$E345+2</f>
         <v>131</v>
       </c>
       <c r="N345" s="14"/>
       <c r="O345" s="5">
-        <f>$E345+4</f>
+        <f t="shared" ref="O345:O372" si="199">$E345+4</f>
         <v>133</v>
       </c>
       <c r="P345" s="14"/>
       <c r="Q345" s="3">
-        <f>$E345+6</f>
+        <f t="shared" ref="Q345:Q372" si="200">$E345+6</f>
         <v>135</v>
       </c>
       <c r="R345" s="14"/>
       <c r="S345" s="5">
-        <f>$E345+8</f>
+        <f t="shared" ref="S345:S372" si="201">$E345+8</f>
         <v>137</v>
       </c>
       <c r="T345" s="14"/>
       <c r="U345" s="3">
-        <f>$E345+11</f>
+        <f t="shared" ref="U345:U372" si="202">$E345+11</f>
         <v>140</v>
       </c>
       <c r="V345" s="14"/>
       <c r="W345" s="5">
-        <f>$E345+15</f>
+        <f t="shared" ref="W345:W372" si="203">$E345+15</f>
         <v>144</v>
       </c>
       <c r="X345" s="14"/>
       <c r="Y345" s="3">
-        <f>$E345+17</f>
+        <f t="shared" ref="Y345:Y372" si="204">$E345+17</f>
         <v>146</v>
       </c>
       <c r="Z345" s="14"/>
       <c r="AA345" s="5">
-        <f>$E345+19</f>
+        <f t="shared" ref="AA345:AA372" si="205">$E345+19</f>
         <v>148</v>
       </c>
       <c r="AB345" s="14"/>
       <c r="AC345" s="3">
-        <f>$E345+21</f>
+        <f t="shared" ref="AC345:AC372" si="206">$E345+21</f>
         <v>150</v>
       </c>
       <c r="AD345" s="14"/>
       <c r="AE345" s="5">
-        <f>$E345+24</f>
+        <f t="shared" ref="AE345:AE372" si="207">$E345+24</f>
         <v>153</v>
       </c>
       <c r="AF345" s="14"/>
       <c r="AG345" s="3">
-        <f>$E345+27</f>
+        <f t="shared" ref="AG345:AG372" si="208">$E345+27</f>
         <v>156</v>
       </c>
       <c r="AH345" s="14"/>
     </row>
-    <row r="346" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>351</v>
       </c>
@@ -45091,74 +45091,74 @@
         <v>33</v>
       </c>
       <c r="I346" s="3">
-        <f>$E346+0</f>
+        <f t="shared" si="196"/>
         <v>130</v>
       </c>
       <c r="J346" s="14">
         <v>11600000000</v>
       </c>
       <c r="K346" s="5">
-        <f>$E346+1</f>
+        <f t="shared" si="197"/>
         <v>131</v>
       </c>
       <c r="L346" s="14"/>
       <c r="M346" s="3">
-        <f>$E346+2</f>
+        <f t="shared" si="198"/>
         <v>132</v>
       </c>
       <c r="N346" s="14"/>
       <c r="O346" s="5">
-        <f>$E346+4</f>
+        <f t="shared" si="199"/>
         <v>134</v>
       </c>
       <c r="P346" s="14"/>
       <c r="Q346" s="3">
-        <f>$E346+6</f>
+        <f t="shared" si="200"/>
         <v>136</v>
       </c>
       <c r="R346" s="14"/>
       <c r="S346" s="5">
-        <f>$E346+8</f>
+        <f t="shared" si="201"/>
         <v>138</v>
       </c>
       <c r="T346" s="14"/>
       <c r="U346" s="3">
-        <f>$E346+11</f>
+        <f t="shared" si="202"/>
         <v>141</v>
       </c>
       <c r="V346" s="14"/>
       <c r="W346" s="5">
-        <f>$E346+15</f>
+        <f t="shared" si="203"/>
         <v>145</v>
       </c>
       <c r="X346" s="14"/>
       <c r="Y346" s="3">
-        <f>$E346+17</f>
+        <f t="shared" si="204"/>
         <v>147</v>
       </c>
       <c r="Z346" s="14"/>
       <c r="AA346" s="5">
-        <f>$E346+19</f>
+        <f t="shared" si="205"/>
         <v>149</v>
       </c>
       <c r="AB346" s="14"/>
       <c r="AC346" s="3">
-        <f>$E346+21</f>
+        <f t="shared" si="206"/>
         <v>151</v>
       </c>
       <c r="AD346" s="14"/>
       <c r="AE346" s="5">
-        <f>$E346+24</f>
+        <f t="shared" si="207"/>
         <v>154</v>
       </c>
       <c r="AF346" s="14"/>
       <c r="AG346" s="3">
-        <f>$E346+27</f>
+        <f t="shared" si="208"/>
         <v>157</v>
       </c>
       <c r="AH346" s="14"/>
     </row>
-    <row r="347" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>352</v>
       </c>
@@ -45184,74 +45184,74 @@
         <v>34</v>
       </c>
       <c r="I347" s="3">
-        <f>$E347+0</f>
+        <f t="shared" si="196"/>
         <v>131</v>
       </c>
       <c r="J347" s="14">
         <v>11600000000</v>
       </c>
       <c r="K347" s="5">
-        <f>$E347+1</f>
+        <f t="shared" si="197"/>
         <v>132</v>
       </c>
       <c r="L347" s="14"/>
       <c r="M347" s="3">
-        <f>$E347+2</f>
+        <f t="shared" si="198"/>
         <v>133</v>
       </c>
       <c r="N347" s="14"/>
       <c r="O347" s="5">
-        <f>$E347+4</f>
+        <f t="shared" si="199"/>
         <v>135</v>
       </c>
       <c r="P347" s="14"/>
       <c r="Q347" s="3">
-        <f>$E347+6</f>
+        <f t="shared" si="200"/>
         <v>137</v>
       </c>
       <c r="R347" s="14"/>
       <c r="S347" s="5">
-        <f>$E347+8</f>
+        <f t="shared" si="201"/>
         <v>139</v>
       </c>
       <c r="T347" s="14"/>
       <c r="U347" s="3">
-        <f>$E347+11</f>
+        <f t="shared" si="202"/>
         <v>142</v>
       </c>
       <c r="V347" s="14"/>
       <c r="W347" s="5">
-        <f>$E347+15</f>
+        <f t="shared" si="203"/>
         <v>146</v>
       </c>
       <c r="X347" s="14"/>
       <c r="Y347" s="3">
-        <f>$E347+17</f>
+        <f t="shared" si="204"/>
         <v>148</v>
       </c>
       <c r="Z347" s="14"/>
       <c r="AA347" s="5">
-        <f>$E347+19</f>
+        <f t="shared" si="205"/>
         <v>150</v>
       </c>
       <c r="AB347" s="14"/>
       <c r="AC347" s="3">
-        <f>$E347+21</f>
+        <f t="shared" si="206"/>
         <v>152</v>
       </c>
       <c r="AD347" s="14"/>
       <c r="AE347" s="5">
-        <f>$E347+24</f>
+        <f t="shared" si="207"/>
         <v>155</v>
       </c>
       <c r="AF347" s="14"/>
       <c r="AG347" s="3">
-        <f>$E347+27</f>
+        <f t="shared" si="208"/>
         <v>158</v>
       </c>
       <c r="AH347" s="14"/>
     </row>
-    <row r="348" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>379</v>
       </c>
@@ -45277,74 +45277,74 @@
         <v>34</v>
       </c>
       <c r="I348" s="3">
-        <f>$E348+0</f>
+        <f t="shared" si="196"/>
         <v>130</v>
       </c>
       <c r="J348" s="14">
         <v>3600000000</v>
       </c>
       <c r="K348" s="5">
-        <f>$E348+1</f>
+        <f t="shared" si="197"/>
         <v>131</v>
       </c>
       <c r="L348" s="14"/>
       <c r="M348" s="3">
-        <f>$E348+2</f>
+        <f t="shared" si="198"/>
         <v>132</v>
       </c>
       <c r="N348" s="14"/>
       <c r="O348" s="5">
-        <f>$E348+4</f>
+        <f t="shared" si="199"/>
         <v>134</v>
       </c>
       <c r="P348" s="14"/>
       <c r="Q348" s="3">
-        <f>$E348+6</f>
+        <f t="shared" si="200"/>
         <v>136</v>
       </c>
       <c r="R348" s="14"/>
       <c r="S348" s="5">
-        <f>$E348+8</f>
+        <f t="shared" si="201"/>
         <v>138</v>
       </c>
       <c r="T348" s="14"/>
       <c r="U348" s="3">
-        <f>$E348+11</f>
+        <f t="shared" si="202"/>
         <v>141</v>
       </c>
       <c r="V348" s="14"/>
       <c r="W348" s="5">
-        <f>$E348+15</f>
+        <f t="shared" si="203"/>
         <v>145</v>
       </c>
       <c r="X348" s="14"/>
       <c r="Y348" s="3">
-        <f>$E348+17</f>
+        <f t="shared" si="204"/>
         <v>147</v>
       </c>
       <c r="Z348" s="14"/>
       <c r="AA348" s="5">
-        <f>$E348+19</f>
+        <f t="shared" si="205"/>
         <v>149</v>
       </c>
       <c r="AB348" s="14"/>
       <c r="AC348" s="3">
-        <f>$E348+21</f>
+        <f t="shared" si="206"/>
         <v>151</v>
       </c>
       <c r="AD348" s="14"/>
       <c r="AE348" s="5">
-        <f>$E348+24</f>
+        <f t="shared" si="207"/>
         <v>154</v>
       </c>
       <c r="AF348" s="14"/>
       <c r="AG348" s="3">
-        <f>$E348+27</f>
+        <f t="shared" si="208"/>
         <v>157</v>
       </c>
       <c r="AH348" s="14"/>
     </row>
-    <row r="349" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>380</v>
       </c>
@@ -45370,74 +45370,74 @@
         <v>34</v>
       </c>
       <c r="I349" s="3">
-        <f>$E349+0</f>
+        <f t="shared" si="196"/>
         <v>131</v>
       </c>
       <c r="J349" s="14">
         <v>4800000000</v>
       </c>
       <c r="K349" s="5">
-        <f>$E349+1</f>
+        <f t="shared" si="197"/>
         <v>132</v>
       </c>
       <c r="L349" s="14"/>
       <c r="M349" s="3">
-        <f>$E349+2</f>
+        <f t="shared" si="198"/>
         <v>133</v>
       </c>
       <c r="N349" s="14"/>
       <c r="O349" s="5">
-        <f>$E349+4</f>
+        <f t="shared" si="199"/>
         <v>135</v>
       </c>
       <c r="P349" s="14"/>
       <c r="Q349" s="3">
-        <f>$E349+6</f>
+        <f t="shared" si="200"/>
         <v>137</v>
       </c>
       <c r="R349" s="14"/>
       <c r="S349" s="5">
-        <f>$E349+8</f>
+        <f t="shared" si="201"/>
         <v>139</v>
       </c>
       <c r="T349" s="14"/>
       <c r="U349" s="3">
-        <f>$E349+11</f>
+        <f t="shared" si="202"/>
         <v>142</v>
       </c>
       <c r="V349" s="14"/>
       <c r="W349" s="5">
-        <f>$E349+15</f>
+        <f t="shared" si="203"/>
         <v>146</v>
       </c>
       <c r="X349" s="14"/>
       <c r="Y349" s="3">
-        <f>$E349+17</f>
+        <f t="shared" si="204"/>
         <v>148</v>
       </c>
       <c r="Z349" s="14"/>
       <c r="AA349" s="5">
-        <f>$E349+19</f>
+        <f t="shared" si="205"/>
         <v>150</v>
       </c>
       <c r="AB349" s="14"/>
       <c r="AC349" s="3">
-        <f>$E349+21</f>
+        <f t="shared" si="206"/>
         <v>152</v>
       </c>
       <c r="AD349" s="14"/>
       <c r="AE349" s="5">
-        <f>$E349+24</f>
+        <f t="shared" si="207"/>
         <v>155</v>
       </c>
       <c r="AF349" s="14"/>
       <c r="AG349" s="3">
-        <f>$E349+27</f>
+        <f t="shared" si="208"/>
         <v>158</v>
       </c>
       <c r="AH349" s="14"/>
     </row>
-    <row r="350" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>381</v>
       </c>
@@ -45463,74 +45463,74 @@
         <v>37</v>
       </c>
       <c r="I350" s="3">
-        <f>$E350+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J350" s="14">
         <v>47600000000</v>
       </c>
       <c r="K350" s="5">
-        <f>$E350+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L350" s="14"/>
       <c r="M350" s="3">
-        <f>$E350+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N350" s="14"/>
       <c r="O350" s="5">
-        <f>$E350+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P350" s="14"/>
       <c r="Q350" s="3">
-        <f>$E350+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R350" s="14"/>
       <c r="S350" s="5">
-        <f>$E350+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T350" s="14"/>
       <c r="U350" s="3">
-        <f>$E350+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V350" s="14"/>
       <c r="W350" s="5">
-        <f>$E350+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X350" s="14"/>
       <c r="Y350" s="3">
-        <f>$E350+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z350" s="14"/>
       <c r="AA350" s="5">
-        <f>$E350+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB350" s="14"/>
       <c r="AC350" s="3">
-        <f>$E350+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD350" s="14"/>
       <c r="AE350" s="5">
-        <f>$E350+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF350" s="14"/>
       <c r="AG350" s="3">
-        <f>$E350+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH350" s="14"/>
     </row>
-    <row r="351" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>382</v>
       </c>
@@ -45556,74 +45556,74 @@
         <v>37</v>
       </c>
       <c r="I351" s="3">
-        <f>$E351+0</f>
+        <f t="shared" si="196"/>
         <v>136</v>
       </c>
       <c r="J351" s="14">
         <v>32800000000</v>
       </c>
       <c r="K351" s="5">
-        <f>$E351+1</f>
+        <f t="shared" si="197"/>
         <v>137</v>
       </c>
       <c r="L351" s="14"/>
       <c r="M351" s="3">
-        <f>$E351+2</f>
+        <f t="shared" si="198"/>
         <v>138</v>
       </c>
       <c r="N351" s="14"/>
       <c r="O351" s="5">
-        <f>$E351+4</f>
+        <f t="shared" si="199"/>
         <v>140</v>
       </c>
       <c r="P351" s="14"/>
       <c r="Q351" s="3">
-        <f>$E351+6</f>
+        <f t="shared" si="200"/>
         <v>142</v>
       </c>
       <c r="R351" s="14"/>
       <c r="S351" s="5">
-        <f>$E351+8</f>
+        <f t="shared" si="201"/>
         <v>144</v>
       </c>
       <c r="T351" s="14"/>
       <c r="U351" s="3">
-        <f>$E351+11</f>
+        <f t="shared" si="202"/>
         <v>147</v>
       </c>
       <c r="V351" s="14"/>
       <c r="W351" s="5">
-        <f>$E351+15</f>
+        <f t="shared" si="203"/>
         <v>151</v>
       </c>
       <c r="X351" s="14"/>
       <c r="Y351" s="3">
-        <f>$E351+17</f>
+        <f t="shared" si="204"/>
         <v>153</v>
       </c>
       <c r="Z351" s="14"/>
       <c r="AA351" s="5">
-        <f>$E351+19</f>
+        <f t="shared" si="205"/>
         <v>155</v>
       </c>
       <c r="AB351" s="14"/>
       <c r="AC351" s="3">
-        <f>$E351+21</f>
+        <f t="shared" si="206"/>
         <v>157</v>
       </c>
       <c r="AD351" s="14"/>
       <c r="AE351" s="5">
-        <f>$E351+24</f>
+        <f t="shared" si="207"/>
         <v>160</v>
       </c>
       <c r="AF351" s="14"/>
       <c r="AG351" s="3">
-        <f>$E351+27</f>
+        <f t="shared" si="208"/>
         <v>163</v>
       </c>
       <c r="AH351" s="14"/>
     </row>
-    <row r="352" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>328</v>
       </c>
@@ -45649,74 +45649,74 @@
         <v>34</v>
       </c>
       <c r="I352" s="3">
-        <f>$E352+0</f>
+        <f t="shared" si="196"/>
         <v>132</v>
       </c>
       <c r="J352" s="14">
         <v>6840000000</v>
       </c>
       <c r="K352" s="5">
-        <f>$E352+1</f>
+        <f t="shared" si="197"/>
         <v>133</v>
       </c>
       <c r="L352" s="14"/>
       <c r="M352" s="3">
-        <f>$E352+2</f>
+        <f t="shared" si="198"/>
         <v>134</v>
       </c>
       <c r="N352" s="14"/>
       <c r="O352" s="5">
-        <f>$E352+4</f>
+        <f t="shared" si="199"/>
         <v>136</v>
       </c>
       <c r="P352" s="14"/>
       <c r="Q352" s="3">
-        <f>$E352+6</f>
+        <f t="shared" si="200"/>
         <v>138</v>
       </c>
       <c r="R352" s="14"/>
       <c r="S352" s="5">
-        <f>$E352+8</f>
+        <f t="shared" si="201"/>
         <v>140</v>
       </c>
       <c r="T352" s="14"/>
       <c r="U352" s="3">
-        <f>$E352+11</f>
+        <f t="shared" si="202"/>
         <v>143</v>
       </c>
       <c r="V352" s="14"/>
       <c r="W352" s="5">
-        <f>$E352+15</f>
+        <f t="shared" si="203"/>
         <v>147</v>
       </c>
       <c r="X352" s="14"/>
       <c r="Y352" s="3">
-        <f>$E352+17</f>
+        <f t="shared" si="204"/>
         <v>149</v>
       </c>
       <c r="Z352" s="14"/>
       <c r="AA352" s="5">
-        <f>$E352+19</f>
+        <f t="shared" si="205"/>
         <v>151</v>
       </c>
       <c r="AB352" s="14"/>
       <c r="AC352" s="3">
-        <f>$E352+21</f>
+        <f t="shared" si="206"/>
         <v>153</v>
       </c>
       <c r="AD352" s="14"/>
       <c r="AE352" s="5">
-        <f>$E352+24</f>
+        <f t="shared" si="207"/>
         <v>156</v>
       </c>
       <c r="AF352" s="14"/>
       <c r="AG352" s="3">
-        <f>$E352+27</f>
+        <f t="shared" si="208"/>
         <v>159</v>
       </c>
       <c r="AH352" s="14"/>
     </row>
-    <row r="353" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>344</v>
       </c>
@@ -45742,74 +45742,74 @@
         <v>36</v>
       </c>
       <c r="I353" s="3">
-        <f>$E353+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J353" s="14">
         <v>20700000000</v>
       </c>
       <c r="K353" s="5">
-        <f>$E353+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L353" s="14"/>
       <c r="M353" s="3">
-        <f>$E353+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N353" s="14"/>
       <c r="O353" s="5">
-        <f>$E353+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P353" s="14"/>
       <c r="Q353" s="3">
-        <f>$E353+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R353" s="14"/>
       <c r="S353" s="5">
-        <f>$E353+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T353" s="14"/>
       <c r="U353" s="3">
-        <f>$E353+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V353" s="14"/>
       <c r="W353" s="5">
-        <f>$E353+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X353" s="14"/>
       <c r="Y353" s="3">
-        <f>$E353+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z353" s="14"/>
       <c r="AA353" s="5">
-        <f>$E353+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB353" s="14"/>
       <c r="AC353" s="3">
-        <f>$E353+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD353" s="14"/>
       <c r="AE353" s="5">
-        <f>$E353+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF353" s="14"/>
       <c r="AG353" s="3">
-        <f>$E353+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH353" s="14"/>
     </row>
-    <row r="354" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>360</v>
       </c>
@@ -45835,74 +45835,74 @@
         <v>35</v>
       </c>
       <c r="I354" s="3">
-        <f>$E354+0</f>
+        <f t="shared" si="196"/>
         <v>133</v>
       </c>
       <c r="J354" s="14">
         <v>22800000000</v>
       </c>
       <c r="K354" s="5">
-        <f>$E354+1</f>
+        <f t="shared" si="197"/>
         <v>134</v>
       </c>
       <c r="L354" s="14"/>
       <c r="M354" s="3">
-        <f>$E354+2</f>
+        <f t="shared" si="198"/>
         <v>135</v>
       </c>
       <c r="N354" s="14"/>
       <c r="O354" s="5">
-        <f>$E354+4</f>
+        <f t="shared" si="199"/>
         <v>137</v>
       </c>
       <c r="P354" s="14"/>
       <c r="Q354" s="3">
-        <f>$E354+6</f>
+        <f t="shared" si="200"/>
         <v>139</v>
       </c>
       <c r="R354" s="14"/>
       <c r="S354" s="5">
-        <f>$E354+8</f>
+        <f t="shared" si="201"/>
         <v>141</v>
       </c>
       <c r="T354" s="14"/>
       <c r="U354" s="3">
-        <f>$E354+11</f>
+        <f t="shared" si="202"/>
         <v>144</v>
       </c>
       <c r="V354" s="14"/>
       <c r="W354" s="5">
-        <f>$E354+15</f>
+        <f t="shared" si="203"/>
         <v>148</v>
       </c>
       <c r="X354" s="14"/>
       <c r="Y354" s="3">
-        <f>$E354+17</f>
+        <f t="shared" si="204"/>
         <v>150</v>
       </c>
       <c r="Z354" s="14"/>
       <c r="AA354" s="5">
-        <f>$E354+19</f>
+        <f t="shared" si="205"/>
         <v>152</v>
       </c>
       <c r="AB354" s="14"/>
       <c r="AC354" s="3">
-        <f>$E354+21</f>
+        <f t="shared" si="206"/>
         <v>154</v>
       </c>
       <c r="AD354" s="14"/>
       <c r="AE354" s="5">
-        <f>$E354+24</f>
+        <f t="shared" si="207"/>
         <v>157</v>
       </c>
       <c r="AF354" s="14"/>
       <c r="AG354" s="3">
-        <f>$E354+27</f>
+        <f t="shared" si="208"/>
         <v>160</v>
       </c>
       <c r="AH354" s="14"/>
     </row>
-    <row r="355" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>361</v>
       </c>
@@ -45928,74 +45928,74 @@
         <v>37</v>
       </c>
       <c r="I355" s="3">
-        <f>$E355+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J355" s="14">
         <v>15600000000</v>
       </c>
       <c r="K355" s="5">
-        <f>$E355+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L355" s="14"/>
       <c r="M355" s="3">
-        <f>$E355+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N355" s="14"/>
       <c r="O355" s="5">
-        <f>$E355+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P355" s="14"/>
       <c r="Q355" s="3">
-        <f>$E355+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R355" s="14"/>
       <c r="S355" s="5">
-        <f>$E355+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T355" s="14"/>
       <c r="U355" s="3">
-        <f>$E355+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V355" s="14"/>
       <c r="W355" s="5">
-        <f>$E355+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X355" s="14"/>
       <c r="Y355" s="3">
-        <f>$E355+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z355" s="14"/>
       <c r="AA355" s="5">
-        <f>$E355+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB355" s="14"/>
       <c r="AC355" s="3">
-        <f>$E355+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD355" s="14"/>
       <c r="AE355" s="5">
-        <f>$E355+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF355" s="14"/>
       <c r="AG355" s="3">
-        <f>$E355+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH355" s="14"/>
     </row>
-    <row r="356" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>362</v>
       </c>
@@ -46021,74 +46021,74 @@
         <v>37</v>
       </c>
       <c r="I356" s="3">
-        <f>$E356+0</f>
+        <f t="shared" si="196"/>
         <v>136</v>
       </c>
       <c r="J356" s="14">
         <v>15600000000</v>
       </c>
       <c r="K356" s="5">
-        <f>$E356+1</f>
+        <f t="shared" si="197"/>
         <v>137</v>
       </c>
       <c r="L356" s="14"/>
       <c r="M356" s="3">
-        <f>$E356+2</f>
+        <f t="shared" si="198"/>
         <v>138</v>
       </c>
       <c r="N356" s="14"/>
       <c r="O356" s="5">
-        <f>$E356+4</f>
+        <f t="shared" si="199"/>
         <v>140</v>
       </c>
       <c r="P356" s="14"/>
       <c r="Q356" s="3">
-        <f>$E356+6</f>
+        <f t="shared" si="200"/>
         <v>142</v>
       </c>
       <c r="R356" s="14"/>
       <c r="S356" s="5">
-        <f>$E356+8</f>
+        <f t="shared" si="201"/>
         <v>144</v>
       </c>
       <c r="T356" s="14"/>
       <c r="U356" s="3">
-        <f>$E356+11</f>
+        <f t="shared" si="202"/>
         <v>147</v>
       </c>
       <c r="V356" s="14"/>
       <c r="W356" s="5">
-        <f>$E356+15</f>
+        <f t="shared" si="203"/>
         <v>151</v>
       </c>
       <c r="X356" s="14"/>
       <c r="Y356" s="3">
-        <f>$E356+17</f>
+        <f t="shared" si="204"/>
         <v>153</v>
       </c>
       <c r="Z356" s="14"/>
       <c r="AA356" s="5">
-        <f>$E356+19</f>
+        <f t="shared" si="205"/>
         <v>155</v>
       </c>
       <c r="AB356" s="14"/>
       <c r="AC356" s="3">
-        <f>$E356+21</f>
+        <f t="shared" si="206"/>
         <v>157</v>
       </c>
       <c r="AD356" s="14"/>
       <c r="AE356" s="5">
-        <f>$E356+24</f>
+        <f t="shared" si="207"/>
         <v>160</v>
       </c>
       <c r="AF356" s="14"/>
       <c r="AG356" s="3">
-        <f>$E356+27</f>
+        <f t="shared" si="208"/>
         <v>163</v>
       </c>
       <c r="AH356" s="14"/>
     </row>
-    <row r="357" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>363</v>
       </c>
@@ -46114,74 +46114,74 @@
         <v>33</v>
       </c>
       <c r="I357" s="3">
-        <f>$E357+0</f>
+        <f t="shared" si="196"/>
         <v>130</v>
       </c>
       <c r="J357" s="14">
         <v>6180000000</v>
       </c>
       <c r="K357" s="5">
-        <f>$E357+1</f>
+        <f t="shared" si="197"/>
         <v>131</v>
       </c>
       <c r="L357" s="14"/>
       <c r="M357" s="3">
-        <f>$E357+2</f>
+        <f t="shared" si="198"/>
         <v>132</v>
       </c>
       <c r="N357" s="14"/>
       <c r="O357" s="5">
-        <f>$E357+4</f>
+        <f t="shared" si="199"/>
         <v>134</v>
       </c>
       <c r="P357" s="14"/>
       <c r="Q357" s="3">
-        <f>$E357+6</f>
+        <f t="shared" si="200"/>
         <v>136</v>
       </c>
       <c r="R357" s="14"/>
       <c r="S357" s="5">
-        <f>$E357+8</f>
+        <f t="shared" si="201"/>
         <v>138</v>
       </c>
       <c r="T357" s="14"/>
       <c r="U357" s="3">
-        <f>$E357+11</f>
+        <f t="shared" si="202"/>
         <v>141</v>
       </c>
       <c r="V357" s="14"/>
       <c r="W357" s="5">
-        <f>$E357+15</f>
+        <f t="shared" si="203"/>
         <v>145</v>
       </c>
       <c r="X357" s="14"/>
       <c r="Y357" s="3">
-        <f>$E357+17</f>
+        <f t="shared" si="204"/>
         <v>147</v>
       </c>
       <c r="Z357" s="14"/>
       <c r="AA357" s="5">
-        <f>$E357+19</f>
+        <f t="shared" si="205"/>
         <v>149</v>
       </c>
       <c r="AB357" s="14"/>
       <c r="AC357" s="3">
-        <f>$E357+21</f>
+        <f t="shared" si="206"/>
         <v>151</v>
       </c>
       <c r="AD357" s="14"/>
       <c r="AE357" s="5">
-        <f>$E357+24</f>
+        <f t="shared" si="207"/>
         <v>154</v>
       </c>
       <c r="AF357" s="14"/>
       <c r="AG357" s="3">
-        <f>$E357+27</f>
+        <f t="shared" si="208"/>
         <v>157</v>
       </c>
       <c r="AH357" s="14"/>
     </row>
-    <row r="358" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>364</v>
       </c>
@@ -46207,74 +46207,74 @@
         <v>33</v>
       </c>
       <c r="I358" s="3">
-        <f>$E358+0</f>
+        <f t="shared" si="196"/>
         <v>130</v>
       </c>
       <c r="J358" s="14">
         <v>2860000000</v>
       </c>
       <c r="K358" s="5">
-        <f>$E358+1</f>
+        <f t="shared" si="197"/>
         <v>131</v>
       </c>
       <c r="L358" s="14"/>
       <c r="M358" s="3">
-        <f>$E358+2</f>
+        <f t="shared" si="198"/>
         <v>132</v>
       </c>
       <c r="N358" s="14"/>
       <c r="O358" s="5">
-        <f>$E358+4</f>
+        <f t="shared" si="199"/>
         <v>134</v>
       </c>
       <c r="P358" s="14"/>
       <c r="Q358" s="3">
-        <f>$E358+6</f>
+        <f t="shared" si="200"/>
         <v>136</v>
       </c>
       <c r="R358" s="14"/>
       <c r="S358" s="5">
-        <f>$E358+8</f>
+        <f t="shared" si="201"/>
         <v>138</v>
       </c>
       <c r="T358" s="14"/>
       <c r="U358" s="3">
-        <f>$E358+11</f>
+        <f t="shared" si="202"/>
         <v>141</v>
       </c>
       <c r="V358" s="14"/>
       <c r="W358" s="5">
-        <f>$E358+15</f>
+        <f t="shared" si="203"/>
         <v>145</v>
       </c>
       <c r="X358" s="14"/>
       <c r="Y358" s="3">
-        <f>$E358+17</f>
+        <f t="shared" si="204"/>
         <v>147</v>
       </c>
       <c r="Z358" s="14"/>
       <c r="AA358" s="5">
-        <f>$E358+19</f>
+        <f t="shared" si="205"/>
         <v>149</v>
       </c>
       <c r="AB358" s="14"/>
       <c r="AC358" s="3">
-        <f>$E358+21</f>
+        <f t="shared" si="206"/>
         <v>151</v>
       </c>
       <c r="AD358" s="14"/>
       <c r="AE358" s="5">
-        <f>$E358+24</f>
+        <f t="shared" si="207"/>
         <v>154</v>
       </c>
       <c r="AF358" s="14"/>
       <c r="AG358" s="3">
-        <f>$E358+27</f>
+        <f t="shared" si="208"/>
         <v>157</v>
       </c>
       <c r="AH358" s="14"/>
     </row>
-    <row r="359" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>365</v>
       </c>
@@ -46300,74 +46300,74 @@
         <v>34</v>
       </c>
       <c r="I359" s="3">
-        <f>$E359+0</f>
+        <f t="shared" si="196"/>
         <v>131</v>
       </c>
       <c r="J359" s="14">
         <v>5280000000</v>
       </c>
       <c r="K359" s="5">
-        <f>$E359+1</f>
+        <f t="shared" si="197"/>
         <v>132</v>
       </c>
       <c r="L359" s="14"/>
       <c r="M359" s="3">
-        <f>$E359+2</f>
+        <f t="shared" si="198"/>
         <v>133</v>
       </c>
       <c r="N359" s="14"/>
       <c r="O359" s="5">
-        <f>$E359+4</f>
+        <f t="shared" si="199"/>
         <v>135</v>
       </c>
       <c r="P359" s="14"/>
       <c r="Q359" s="3">
-        <f>$E359+6</f>
+        <f t="shared" si="200"/>
         <v>137</v>
       </c>
       <c r="R359" s="14"/>
       <c r="S359" s="5">
-        <f>$E359+8</f>
+        <f t="shared" si="201"/>
         <v>139</v>
       </c>
       <c r="T359" s="14"/>
       <c r="U359" s="3">
-        <f>$E359+11</f>
+        <f t="shared" si="202"/>
         <v>142</v>
       </c>
       <c r="V359" s="14"/>
       <c r="W359" s="5">
-        <f>$E359+15</f>
+        <f t="shared" si="203"/>
         <v>146</v>
       </c>
       <c r="X359" s="14"/>
       <c r="Y359" s="3">
-        <f>$E359+17</f>
+        <f t="shared" si="204"/>
         <v>148</v>
       </c>
       <c r="Z359" s="14"/>
       <c r="AA359" s="5">
-        <f>$E359+19</f>
+        <f t="shared" si="205"/>
         <v>150</v>
       </c>
       <c r="AB359" s="14"/>
       <c r="AC359" s="3">
-        <f>$E359+21</f>
+        <f t="shared" si="206"/>
         <v>152</v>
       </c>
       <c r="AD359" s="14"/>
       <c r="AE359" s="5">
-        <f>$E359+24</f>
+        <f t="shared" si="207"/>
         <v>155</v>
       </c>
       <c r="AF359" s="14"/>
       <c r="AG359" s="3">
-        <f>$E359+27</f>
+        <f t="shared" si="208"/>
         <v>158</v>
       </c>
       <c r="AH359" s="14"/>
     </row>
-    <row r="360" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>366</v>
       </c>
@@ -46393,74 +46393,74 @@
         <v>35</v>
       </c>
       <c r="I360" s="3">
-        <f>$E360+0</f>
+        <f t="shared" si="196"/>
         <v>132</v>
       </c>
       <c r="J360" s="14">
         <v>5070000000</v>
       </c>
       <c r="K360" s="5">
-        <f>$E360+1</f>
+        <f t="shared" si="197"/>
         <v>133</v>
       </c>
       <c r="L360" s="14"/>
       <c r="M360" s="3">
-        <f>$E360+2</f>
+        <f t="shared" si="198"/>
         <v>134</v>
       </c>
       <c r="N360" s="14"/>
       <c r="O360" s="5">
-        <f>$E360+4</f>
+        <f t="shared" si="199"/>
         <v>136</v>
       </c>
       <c r="P360" s="14"/>
       <c r="Q360" s="3">
-        <f>$E360+6</f>
+        <f t="shared" si="200"/>
         <v>138</v>
       </c>
       <c r="R360" s="14"/>
       <c r="S360" s="5">
-        <f>$E360+8</f>
+        <f t="shared" si="201"/>
         <v>140</v>
       </c>
       <c r="T360" s="14"/>
       <c r="U360" s="3">
-        <f>$E360+11</f>
+        <f t="shared" si="202"/>
         <v>143</v>
       </c>
       <c r="V360" s="14"/>
       <c r="W360" s="5">
-        <f>$E360+15</f>
+        <f t="shared" si="203"/>
         <v>147</v>
       </c>
       <c r="X360" s="14"/>
       <c r="Y360" s="3">
-        <f>$E360+17</f>
+        <f t="shared" si="204"/>
         <v>149</v>
       </c>
       <c r="Z360" s="14"/>
       <c r="AA360" s="5">
-        <f>$E360+19</f>
+        <f t="shared" si="205"/>
         <v>151</v>
       </c>
       <c r="AB360" s="14"/>
       <c r="AC360" s="3">
-        <f>$E360+21</f>
+        <f t="shared" si="206"/>
         <v>153</v>
       </c>
       <c r="AD360" s="14"/>
       <c r="AE360" s="5">
-        <f>$E360+24</f>
+        <f t="shared" si="207"/>
         <v>156</v>
       </c>
       <c r="AF360" s="14"/>
       <c r="AG360" s="3">
-        <f>$E360+27</f>
+        <f t="shared" si="208"/>
         <v>159</v>
       </c>
       <c r="AH360" s="14"/>
     </row>
-    <row r="361" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>367</v>
       </c>
@@ -46486,74 +46486,74 @@
         <v>35</v>
       </c>
       <c r="I361" s="3">
-        <f>$E361+0</f>
+        <f t="shared" si="196"/>
         <v>132</v>
       </c>
       <c r="J361" s="14">
         <v>14100000000</v>
       </c>
       <c r="K361" s="5">
-        <f>$E361+1</f>
+        <f t="shared" si="197"/>
         <v>133</v>
       </c>
       <c r="L361" s="14"/>
       <c r="M361" s="3">
-        <f>$E361+2</f>
+        <f t="shared" si="198"/>
         <v>134</v>
       </c>
       <c r="N361" s="14"/>
       <c r="O361" s="5">
-        <f>$E361+4</f>
+        <f t="shared" si="199"/>
         <v>136</v>
       </c>
       <c r="P361" s="14"/>
       <c r="Q361" s="3">
-        <f>$E361+6</f>
+        <f t="shared" si="200"/>
         <v>138</v>
       </c>
       <c r="R361" s="14"/>
       <c r="S361" s="5">
-        <f>$E361+8</f>
+        <f t="shared" si="201"/>
         <v>140</v>
       </c>
       <c r="T361" s="14"/>
       <c r="U361" s="3">
-        <f>$E361+11</f>
+        <f t="shared" si="202"/>
         <v>143</v>
       </c>
       <c r="V361" s="14"/>
       <c r="W361" s="5">
-        <f>$E361+15</f>
+        <f t="shared" si="203"/>
         <v>147</v>
       </c>
       <c r="X361" s="14"/>
       <c r="Y361" s="3">
-        <f>$E361+17</f>
+        <f t="shared" si="204"/>
         <v>149</v>
       </c>
       <c r="Z361" s="14"/>
       <c r="AA361" s="5">
-        <f>$E361+19</f>
+        <f t="shared" si="205"/>
         <v>151</v>
       </c>
       <c r="AB361" s="14"/>
       <c r="AC361" s="3">
-        <f>$E361+21</f>
+        <f t="shared" si="206"/>
         <v>153</v>
       </c>
       <c r="AD361" s="14"/>
       <c r="AE361" s="5">
-        <f>$E361+24</f>
+        <f t="shared" si="207"/>
         <v>156</v>
       </c>
       <c r="AF361" s="14"/>
       <c r="AG361" s="3">
-        <f>$E361+27</f>
+        <f t="shared" si="208"/>
         <v>159</v>
       </c>
       <c r="AH361" s="14"/>
     </row>
-    <row r="362" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>368</v>
       </c>
@@ -46579,74 +46579,74 @@
         <v>34</v>
       </c>
       <c r="I362" s="3">
-        <f>$E362+0</f>
+        <f t="shared" si="196"/>
         <v>132</v>
       </c>
       <c r="J362" s="14">
         <v>4610000000</v>
       </c>
       <c r="K362" s="5">
-        <f>$E362+1</f>
+        <f t="shared" si="197"/>
         <v>133</v>
       </c>
       <c r="L362" s="14"/>
       <c r="M362" s="3">
-        <f>$E362+2</f>
+        <f t="shared" si="198"/>
         <v>134</v>
       </c>
       <c r="N362" s="14"/>
       <c r="O362" s="5">
-        <f>$E362+4</f>
+        <f t="shared" si="199"/>
         <v>136</v>
       </c>
       <c r="P362" s="14"/>
       <c r="Q362" s="3">
-        <f>$E362+6</f>
+        <f t="shared" si="200"/>
         <v>138</v>
       </c>
       <c r="R362" s="14"/>
       <c r="S362" s="5">
-        <f>$E362+8</f>
+        <f t="shared" si="201"/>
         <v>140</v>
       </c>
       <c r="T362" s="14"/>
       <c r="U362" s="3">
-        <f>$E362+11</f>
+        <f t="shared" si="202"/>
         <v>143</v>
       </c>
       <c r="V362" s="14"/>
       <c r="W362" s="5">
-        <f>$E362+15</f>
+        <f t="shared" si="203"/>
         <v>147</v>
       </c>
       <c r="X362" s="14"/>
       <c r="Y362" s="3">
-        <f>$E362+17</f>
+        <f t="shared" si="204"/>
         <v>149</v>
       </c>
       <c r="Z362" s="14"/>
       <c r="AA362" s="5">
-        <f>$E362+19</f>
+        <f t="shared" si="205"/>
         <v>151</v>
       </c>
       <c r="AB362" s="14"/>
       <c r="AC362" s="3">
-        <f>$E362+21</f>
+        <f t="shared" si="206"/>
         <v>153</v>
       </c>
       <c r="AD362" s="14"/>
       <c r="AE362" s="5">
-        <f>$E362+24</f>
+        <f t="shared" si="207"/>
         <v>156</v>
       </c>
       <c r="AF362" s="14"/>
       <c r="AG362" s="3">
-        <f>$E362+27</f>
+        <f t="shared" si="208"/>
         <v>159</v>
       </c>
       <c r="AH362" s="14"/>
     </row>
-    <row r="363" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>369</v>
       </c>
@@ -46672,74 +46672,74 @@
         <v>35</v>
       </c>
       <c r="I363" s="3">
-        <f>$E363+0</f>
+        <f t="shared" si="196"/>
         <v>133</v>
       </c>
       <c r="J363" s="14">
         <v>22800000000</v>
       </c>
       <c r="K363" s="5">
-        <f>$E363+1</f>
+        <f t="shared" si="197"/>
         <v>134</v>
       </c>
       <c r="L363" s="14"/>
       <c r="M363" s="3">
-        <f>$E363+2</f>
+        <f t="shared" si="198"/>
         <v>135</v>
       </c>
       <c r="N363" s="14"/>
       <c r="O363" s="5">
-        <f>$E363+4</f>
+        <f t="shared" si="199"/>
         <v>137</v>
       </c>
       <c r="P363" s="14"/>
       <c r="Q363" s="3">
-        <f>$E363+6</f>
+        <f t="shared" si="200"/>
         <v>139</v>
       </c>
       <c r="R363" s="14"/>
       <c r="S363" s="5">
-        <f>$E363+8</f>
+        <f t="shared" si="201"/>
         <v>141</v>
       </c>
       <c r="T363" s="14"/>
       <c r="U363" s="3">
-        <f>$E363+11</f>
+        <f t="shared" si="202"/>
         <v>144</v>
       </c>
       <c r="V363" s="14"/>
       <c r="W363" s="5">
-        <f>$E363+15</f>
+        <f t="shared" si="203"/>
         <v>148</v>
       </c>
       <c r="X363" s="14"/>
       <c r="Y363" s="3">
-        <f>$E363+17</f>
+        <f t="shared" si="204"/>
         <v>150</v>
       </c>
       <c r="Z363" s="14"/>
       <c r="AA363" s="5">
-        <f>$E363+19</f>
+        <f t="shared" si="205"/>
         <v>152</v>
       </c>
       <c r="AB363" s="14"/>
       <c r="AC363" s="3">
-        <f>$E363+21</f>
+        <f t="shared" si="206"/>
         <v>154</v>
       </c>
       <c r="AD363" s="14"/>
       <c r="AE363" s="5">
-        <f>$E363+24</f>
+        <f t="shared" si="207"/>
         <v>157</v>
       </c>
       <c r="AF363" s="14"/>
       <c r="AG363" s="3">
-        <f>$E363+27</f>
+        <f t="shared" si="208"/>
         <v>160</v>
       </c>
       <c r="AH363" s="14"/>
     </row>
-    <row r="364" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>370</v>
       </c>
@@ -46765,74 +46765,74 @@
         <v>35</v>
       </c>
       <c r="I364" s="3">
-        <f>$E364+0</f>
+        <f t="shared" si="196"/>
         <v>133</v>
       </c>
       <c r="J364" s="14">
         <v>7440000000</v>
       </c>
       <c r="K364" s="5">
-        <f>$E364+1</f>
+        <f t="shared" si="197"/>
         <v>134</v>
       </c>
       <c r="L364" s="14"/>
       <c r="M364" s="3">
-        <f>$E364+2</f>
+        <f t="shared" si="198"/>
         <v>135</v>
       </c>
       <c r="N364" s="14"/>
       <c r="O364" s="5">
-        <f>$E364+4</f>
+        <f t="shared" si="199"/>
         <v>137</v>
       </c>
       <c r="P364" s="14"/>
       <c r="Q364" s="3">
-        <f>$E364+6</f>
+        <f t="shared" si="200"/>
         <v>139</v>
       </c>
       <c r="R364" s="14"/>
       <c r="S364" s="5">
-        <f>$E364+8</f>
+        <f t="shared" si="201"/>
         <v>141</v>
       </c>
       <c r="T364" s="14"/>
       <c r="U364" s="3">
-        <f>$E364+11</f>
+        <f t="shared" si="202"/>
         <v>144</v>
       </c>
       <c r="V364" s="14"/>
       <c r="W364" s="5">
-        <f>$E364+15</f>
+        <f t="shared" si="203"/>
         <v>148</v>
       </c>
       <c r="X364" s="14"/>
       <c r="Y364" s="3">
-        <f>$E364+17</f>
+        <f t="shared" si="204"/>
         <v>150</v>
       </c>
       <c r="Z364" s="14"/>
       <c r="AA364" s="5">
-        <f>$E364+19</f>
+        <f t="shared" si="205"/>
         <v>152</v>
       </c>
       <c r="AB364" s="14"/>
       <c r="AC364" s="3">
-        <f>$E364+21</f>
+        <f t="shared" si="206"/>
         <v>154</v>
       </c>
       <c r="AD364" s="14"/>
       <c r="AE364" s="5">
-        <f>$E364+24</f>
+        <f t="shared" si="207"/>
         <v>157</v>
       </c>
       <c r="AF364" s="14"/>
       <c r="AG364" s="3">
-        <f>$E364+27</f>
+        <f t="shared" si="208"/>
         <v>160</v>
       </c>
       <c r="AH364" s="14"/>
     </row>
-    <row r="365" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>371</v>
       </c>
@@ -46858,74 +46858,74 @@
         <v>35</v>
       </c>
       <c r="I365" s="3">
-        <f>$E365+0</f>
+        <f t="shared" si="196"/>
         <v>134</v>
       </c>
       <c r="J365" s="14">
         <v>7440000000</v>
       </c>
       <c r="K365" s="5">
-        <f>$E365+1</f>
+        <f t="shared" si="197"/>
         <v>135</v>
       </c>
       <c r="L365" s="14"/>
       <c r="M365" s="3">
-        <f>$E365+2</f>
+        <f t="shared" si="198"/>
         <v>136</v>
       </c>
       <c r="N365" s="14"/>
       <c r="O365" s="5">
-        <f>$E365+4</f>
+        <f t="shared" si="199"/>
         <v>138</v>
       </c>
       <c r="P365" s="14"/>
       <c r="Q365" s="3">
-        <f>$E365+6</f>
+        <f t="shared" si="200"/>
         <v>140</v>
       </c>
       <c r="R365" s="14"/>
       <c r="S365" s="5">
-        <f>$E365+8</f>
+        <f t="shared" si="201"/>
         <v>142</v>
       </c>
       <c r="T365" s="14"/>
       <c r="U365" s="3">
-        <f>$E365+11</f>
+        <f t="shared" si="202"/>
         <v>145</v>
       </c>
       <c r="V365" s="14"/>
       <c r="W365" s="5">
-        <f>$E365+15</f>
+        <f t="shared" si="203"/>
         <v>149</v>
       </c>
       <c r="X365" s="14"/>
       <c r="Y365" s="3">
-        <f>$E365+17</f>
+        <f t="shared" si="204"/>
         <v>151</v>
       </c>
       <c r="Z365" s="14"/>
       <c r="AA365" s="5">
-        <f>$E365+19</f>
+        <f t="shared" si="205"/>
         <v>153</v>
       </c>
       <c r="AB365" s="14"/>
       <c r="AC365" s="3">
-        <f>$E365+21</f>
+        <f t="shared" si="206"/>
         <v>155</v>
       </c>
       <c r="AD365" s="14"/>
       <c r="AE365" s="5">
-        <f>$E365+24</f>
+        <f t="shared" si="207"/>
         <v>158</v>
       </c>
       <c r="AF365" s="14"/>
       <c r="AG365" s="3">
-        <f>$E365+27</f>
+        <f t="shared" si="208"/>
         <v>161</v>
       </c>
       <c r="AH365" s="14"/>
     </row>
-    <row r="366" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>372</v>
       </c>
@@ -46951,74 +46951,74 @@
         <v>36</v>
       </c>
       <c r="I366" s="3">
-        <f>$E366+0</f>
+        <f t="shared" si="196"/>
         <v>134</v>
       </c>
       <c r="J366" s="14">
         <v>10600000000</v>
       </c>
       <c r="K366" s="5">
-        <f>$E366+1</f>
+        <f t="shared" si="197"/>
         <v>135</v>
       </c>
       <c r="L366" s="14"/>
       <c r="M366" s="3">
-        <f>$E366+2</f>
+        <f t="shared" si="198"/>
         <v>136</v>
       </c>
       <c r="N366" s="14"/>
       <c r="O366" s="5">
-        <f>$E366+4</f>
+        <f t="shared" si="199"/>
         <v>138</v>
       </c>
       <c r="P366" s="14"/>
       <c r="Q366" s="3">
-        <f>$E366+6</f>
+        <f t="shared" si="200"/>
         <v>140</v>
       </c>
       <c r="R366" s="14"/>
       <c r="S366" s="5">
-        <f>$E366+8</f>
+        <f t="shared" si="201"/>
         <v>142</v>
       </c>
       <c r="T366" s="14"/>
       <c r="U366" s="3">
-        <f>$E366+11</f>
+        <f t="shared" si="202"/>
         <v>145</v>
       </c>
       <c r="V366" s="14"/>
       <c r="W366" s="5">
-        <f>$E366+15</f>
+        <f t="shared" si="203"/>
         <v>149</v>
       </c>
       <c r="X366" s="14"/>
       <c r="Y366" s="3">
-        <f>$E366+17</f>
+        <f t="shared" si="204"/>
         <v>151</v>
       </c>
       <c r="Z366" s="14"/>
       <c r="AA366" s="5">
-        <f>$E366+19</f>
+        <f t="shared" si="205"/>
         <v>153</v>
       </c>
       <c r="AB366" s="14"/>
       <c r="AC366" s="3">
-        <f>$E366+21</f>
+        <f t="shared" si="206"/>
         <v>155</v>
       </c>
       <c r="AD366" s="14"/>
       <c r="AE366" s="5">
-        <f>$E366+24</f>
+        <f t="shared" si="207"/>
         <v>158</v>
       </c>
       <c r="AF366" s="14"/>
       <c r="AG366" s="3">
-        <f>$E366+27</f>
+        <f t="shared" si="208"/>
         <v>161</v>
       </c>
       <c r="AH366" s="14"/>
     </row>
-    <row r="367" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>373</v>
       </c>
@@ -47044,74 +47044,74 @@
         <v>37</v>
       </c>
       <c r="I367" s="3">
-        <f>$E367+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J367" s="14">
         <v>48800000000</v>
       </c>
       <c r="K367" s="5">
-        <f>$E367+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L367" s="14"/>
       <c r="M367" s="3">
-        <f>$E367+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N367" s="14"/>
       <c r="O367" s="5">
-        <f>$E367+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P367" s="14"/>
       <c r="Q367" s="3">
-        <f>$E367+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R367" s="14"/>
       <c r="S367" s="5">
-        <f>$E367+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T367" s="14"/>
       <c r="U367" s="3">
-        <f>$E367+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V367" s="14"/>
       <c r="W367" s="5">
-        <f>$E367+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X367" s="14"/>
       <c r="Y367" s="3">
-        <f>$E367+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z367" s="14"/>
       <c r="AA367" s="5">
-        <f>$E367+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB367" s="14"/>
       <c r="AC367" s="3">
-        <f>$E367+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD367" s="14"/>
       <c r="AE367" s="5">
-        <f>$E367+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF367" s="14"/>
       <c r="AG367" s="3">
-        <f>$E367+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH367" s="14"/>
     </row>
-    <row r="368" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>374</v>
       </c>
@@ -47137,74 +47137,74 @@
         <v>36</v>
       </c>
       <c r="I368" s="3">
-        <f>$E368+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J368" s="14">
         <v>6180000000</v>
       </c>
       <c r="K368" s="5">
-        <f>$E368+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L368" s="14"/>
       <c r="M368" s="3">
-        <f>$E368+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N368" s="14"/>
       <c r="O368" s="5">
-        <f>$E368+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P368" s="14"/>
       <c r="Q368" s="3">
-        <f>$E368+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R368" s="14"/>
       <c r="S368" s="5">
-        <f>$E368+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T368" s="14"/>
       <c r="U368" s="3">
-        <f>$E368+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V368" s="14"/>
       <c r="W368" s="5">
-        <f>$E368+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X368" s="14"/>
       <c r="Y368" s="3">
-        <f>$E368+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z368" s="14"/>
       <c r="AA368" s="5">
-        <f>$E368+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB368" s="14"/>
       <c r="AC368" s="3">
-        <f>$E368+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD368" s="14"/>
       <c r="AE368" s="5">
-        <f>$E368+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF368" s="14"/>
       <c r="AG368" s="3">
-        <f>$E368+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH368" s="14"/>
     </row>
-    <row r="369" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>375</v>
       </c>
@@ -47230,74 +47230,74 @@
         <v>37</v>
       </c>
       <c r="I369" s="3">
-        <f>$E369+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J369" s="14">
         <v>14800000000</v>
       </c>
       <c r="K369" s="5">
-        <f>$E369+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L369" s="14"/>
       <c r="M369" s="3">
-        <f>$E369+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N369" s="14"/>
       <c r="O369" s="5">
-        <f>$E369+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P369" s="14"/>
       <c r="Q369" s="3">
-        <f>$E369+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R369" s="14"/>
       <c r="S369" s="5">
-        <f>$E369+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T369" s="14"/>
       <c r="U369" s="3">
-        <f>$E369+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V369" s="14"/>
       <c r="W369" s="5">
-        <f>$E369+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X369" s="14"/>
       <c r="Y369" s="3">
-        <f>$E369+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z369" s="14"/>
       <c r="AA369" s="5">
-        <f>$E369+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB369" s="14"/>
       <c r="AC369" s="3">
-        <f>$E369+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD369" s="14"/>
       <c r="AE369" s="5">
-        <f>$E369+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF369" s="14"/>
       <c r="AG369" s="3">
-        <f>$E369+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH369" s="14"/>
     </row>
-    <row r="370" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>376</v>
       </c>
@@ -47323,74 +47323,74 @@
         <v>37</v>
       </c>
       <c r="I370" s="3">
-        <f>$E370+0</f>
+        <f t="shared" si="196"/>
         <v>135</v>
       </c>
       <c r="J370" s="14">
         <v>11200000000</v>
       </c>
       <c r="K370" s="5">
-        <f>$E370+1</f>
+        <f t="shared" si="197"/>
         <v>136</v>
       </c>
       <c r="L370" s="14"/>
       <c r="M370" s="3">
-        <f>$E370+2</f>
+        <f t="shared" si="198"/>
         <v>137</v>
       </c>
       <c r="N370" s="14"/>
       <c r="O370" s="5">
-        <f>$E370+4</f>
+        <f t="shared" si="199"/>
         <v>139</v>
       </c>
       <c r="P370" s="14"/>
       <c r="Q370" s="3">
-        <f>$E370+6</f>
+        <f t="shared" si="200"/>
         <v>141</v>
       </c>
       <c r="R370" s="14"/>
       <c r="S370" s="5">
-        <f>$E370+8</f>
+        <f t="shared" si="201"/>
         <v>143</v>
       </c>
       <c r="T370" s="14"/>
       <c r="U370" s="3">
-        <f>$E370+11</f>
+        <f t="shared" si="202"/>
         <v>146</v>
       </c>
       <c r="V370" s="14"/>
       <c r="W370" s="5">
-        <f>$E370+15</f>
+        <f t="shared" si="203"/>
         <v>150</v>
       </c>
       <c r="X370" s="14"/>
       <c r="Y370" s="3">
-        <f>$E370+17</f>
+        <f t="shared" si="204"/>
         <v>152</v>
       </c>
       <c r="Z370" s="14"/>
       <c r="AA370" s="5">
-        <f>$E370+19</f>
+        <f t="shared" si="205"/>
         <v>154</v>
       </c>
       <c r="AB370" s="14"/>
       <c r="AC370" s="3">
-        <f>$E370+21</f>
+        <f t="shared" si="206"/>
         <v>156</v>
       </c>
       <c r="AD370" s="14"/>
       <c r="AE370" s="5">
-        <f>$E370+24</f>
+        <f t="shared" si="207"/>
         <v>159</v>
       </c>
       <c r="AF370" s="14"/>
       <c r="AG370" s="3">
-        <f>$E370+27</f>
+        <f t="shared" si="208"/>
         <v>162</v>
       </c>
       <c r="AH370" s="14"/>
     </row>
-    <row r="371" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>377</v>
       </c>
@@ -47416,74 +47416,74 @@
         <v>37</v>
       </c>
       <c r="I371" s="3">
-        <f>$E371+0</f>
+        <f t="shared" si="196"/>
         <v>136</v>
       </c>
       <c r="J371" s="14">
         <v>100000000000</v>
       </c>
       <c r="K371" s="5">
-        <f>$E371+1</f>
+        <f t="shared" si="197"/>
         <v>137</v>
       </c>
       <c r="L371" s="14"/>
       <c r="M371" s="3">
-        <f>$E371+2</f>
+        <f t="shared" si="198"/>
         <v>138</v>
       </c>
       <c r="N371" s="14"/>
       <c r="O371" s="5">
-        <f>$E371+4</f>
+        <f t="shared" si="199"/>
         <v>140</v>
       </c>
       <c r="P371" s="14"/>
       <c r="Q371" s="3">
-        <f>$E371+6</f>
+        <f t="shared" si="200"/>
         <v>142</v>
       </c>
       <c r="R371" s="14"/>
       <c r="S371" s="5">
-        <f>$E371+8</f>
+        <f t="shared" si="201"/>
         <v>144</v>
       </c>
       <c r="T371" s="14"/>
       <c r="U371" s="3">
-        <f>$E371+11</f>
+        <f t="shared" si="202"/>
         <v>147</v>
       </c>
       <c r="V371" s="14"/>
       <c r="W371" s="5">
-        <f>$E371+15</f>
+        <f t="shared" si="203"/>
         <v>151</v>
       </c>
       <c r="X371" s="14"/>
       <c r="Y371" s="3">
-        <f>$E371+17</f>
+        <f t="shared" si="204"/>
         <v>153</v>
       </c>
       <c r="Z371" s="14"/>
       <c r="AA371" s="5">
-        <f>$E371+19</f>
+        <f t="shared" si="205"/>
         <v>155</v>
       </c>
       <c r="AB371" s="14"/>
       <c r="AC371" s="3">
-        <f>$E371+21</f>
+        <f t="shared" si="206"/>
         <v>157</v>
       </c>
       <c r="AD371" s="14"/>
       <c r="AE371" s="5">
-        <f>$E371+24</f>
+        <f t="shared" si="207"/>
         <v>160</v>
       </c>
       <c r="AF371" s="14"/>
       <c r="AG371" s="3">
-        <f>$E371+27</f>
+        <f t="shared" si="208"/>
         <v>163</v>
       </c>
       <c r="AH371" s="14"/>
     </row>
-    <row r="372" spans="1:34" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:34" ht="28.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>378</v>
       </c>
@@ -47509,69 +47509,69 @@
         <v>38</v>
       </c>
       <c r="I372" s="3">
-        <f>$E372+0</f>
+        <f t="shared" si="196"/>
         <v>136</v>
       </c>
       <c r="J372" s="14">
         <v>32800000000</v>
       </c>
       <c r="K372" s="5">
-        <f>$E372+1</f>
+        <f t="shared" si="197"/>
         <v>137</v>
       </c>
       <c r="L372" s="14"/>
       <c r="M372" s="3">
-        <f>$E372+2</f>
+        <f t="shared" si="198"/>
         <v>138</v>
       </c>
       <c r="N372" s="14"/>
       <c r="O372" s="5">
-        <f>$E372+4</f>
+        <f t="shared" si="199"/>
         <v>140</v>
       </c>
       <c r="P372" s="14"/>
       <c r="Q372" s="3">
-        <f>$E372+6</f>
+        <f t="shared" si="200"/>
         <v>142</v>
       </c>
       <c r="R372" s="14"/>
       <c r="S372" s="5">
-        <f>$E372+8</f>
+        <f t="shared" si="201"/>
         <v>144</v>
       </c>
       <c r="T372" s="14"/>
       <c r="U372" s="3">
-        <f>$E372+11</f>
+        <f t="shared" si="202"/>
         <v>147</v>
       </c>
       <c r="V372" s="14"/>
       <c r="W372" s="5">
-        <f>$E372+15</f>
+        <f t="shared" si="203"/>
         <v>151</v>
       </c>
       <c r="X372" s="14"/>
       <c r="Y372" s="3">
-        <f>$E372+17</f>
+        <f t="shared" si="204"/>
         <v>153</v>
       </c>
       <c r="Z372" s="14"/>
       <c r="AA372" s="5">
-        <f>$E372+19</f>
+        <f t="shared" si="205"/>
         <v>155</v>
       </c>
       <c r="AB372" s="14"/>
       <c r="AC372" s="3">
-        <f>$E372+21</f>
+        <f t="shared" si="206"/>
         <v>157</v>
       </c>
       <c r="AD372" s="14"/>
       <c r="AE372" s="5">
-        <f>$E372+24</f>
+        <f t="shared" si="207"/>
         <v>160</v>
       </c>
       <c r="AF372" s="14"/>
       <c r="AG372" s="3">
-        <f>$E372+27</f>
+        <f t="shared" si="208"/>
         <v>163</v>
       </c>
       <c r="AH372" s="14"/>
@@ -47580,7 +47580,7 @@
   <autoFilter ref="A1:AH372" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="INFINITE PRIME"/>
+        <filter val="ICON TM"/>
       </filters>
     </filterColumn>
     <filterColumn colId="8" showButton="0"/>
@@ -47601,6 +47601,11 @@
     </sortState>
   </autoFilter>
   <mergeCells count="21">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="AC1:AD1"/>
     <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AG1:AH1"/>
@@ -47617,11 +47622,6 @@
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
